--- a/data/extracted/inventory-receipts/REP CONTENEDR QATAR PREMIUM 27.XLSX
+++ b/data/extracted/inventory-receipts/REP CONTENEDR QATAR PREMIUM 27.XLSX
@@ -1,18 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AF0036-DESKTOP\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\txpacifico\txp-inventory\data\extracted\inventory-receipts\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{083B6E16-175D-44C1-A46E-D97C959ABED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20370" windowHeight="9750"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="IBUM" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -3734,7 +3736,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="###,###,###,###,##0.#0"/>
   </numFmts>
@@ -3775,11 +3777,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -4060,50 +4061,50 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L975"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="3.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" style="1" customWidth="1"/>
-    <col min="8" max="12" width="10.7109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="3.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="4.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" style="1" customWidth="1"/>
+    <col min="8" max="12" width="10.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -4141,12 +4142,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -4184,7 +4185,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
@@ -4222,7 +4223,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
@@ -4260,7 +4261,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -4298,7 +4299,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
@@ -4336,7 +4337,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
@@ -4374,7 +4375,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -4412,7 +4413,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>19</v>
       </c>
@@ -4450,7 +4451,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
@@ -4488,7 +4489,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
@@ -4526,7 +4527,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>19</v>
       </c>
@@ -4564,7 +4565,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>19</v>
       </c>
@@ -4602,7 +4603,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>19</v>
       </c>
@@ -4640,7 +4641,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
@@ -4678,7 +4679,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
@@ -4716,7 +4717,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>19</v>
       </c>
@@ -4754,7 +4755,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>19</v>
       </c>
@@ -4792,7 +4793,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>19</v>
       </c>
@@ -4830,7 +4831,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>19</v>
       </c>
@@ -4868,7 +4869,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>19</v>
       </c>
@@ -4906,7 +4907,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>19</v>
       </c>
@@ -4944,7 +4945,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>19</v>
       </c>
@@ -4982,7 +4983,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>19</v>
       </c>
@@ -5020,7 +5021,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>19</v>
       </c>
@@ -5058,7 +5059,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>19</v>
       </c>
@@ -5096,7 +5097,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>19</v>
       </c>
@@ -5134,7 +5135,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>19</v>
       </c>
@@ -5172,7 +5173,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>19</v>
       </c>
@@ -5210,7 +5211,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>19</v>
       </c>
@@ -5248,7 +5249,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>19</v>
       </c>
@@ -5286,7 +5287,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>19</v>
       </c>
@@ -5324,7 +5325,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>19</v>
       </c>
@@ -5362,7 +5363,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>19</v>
       </c>
@@ -5400,7 +5401,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>19</v>
       </c>
@@ -5438,7 +5439,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F41" s="1" t="s">
         <v>93</v>
       </c>
@@ -5458,7 +5459,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F42" s="1" t="s">
         <v>95</v>
       </c>
@@ -5478,7 +5479,7 @@
         <v>817.3</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>19</v>
       </c>
@@ -5516,7 +5517,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>19</v>
       </c>
@@ -5554,7 +5555,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>19</v>
       </c>
@@ -5592,7 +5593,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>19</v>
       </c>
@@ -5630,7 +5631,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>19</v>
       </c>
@@ -5668,7 +5669,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>19</v>
       </c>
@@ -5706,7 +5707,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>19</v>
       </c>
@@ -5744,7 +5745,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>19</v>
       </c>
@@ -5782,7 +5783,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>19</v>
       </c>
@@ -5820,7 +5821,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>19</v>
       </c>
@@ -5858,7 +5859,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>19</v>
       </c>
@@ -5896,7 +5897,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>19</v>
       </c>
@@ -5934,7 +5935,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>19</v>
       </c>
@@ -5972,7 +5973,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>19</v>
       </c>
@@ -6010,7 +6011,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>19</v>
       </c>
@@ -6048,7 +6049,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>19</v>
       </c>
@@ -6086,7 +6087,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>19</v>
       </c>
@@ -6124,7 +6125,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>19</v>
       </c>
@@ -6162,7 +6163,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>19</v>
       </c>
@@ -6200,7 +6201,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>19</v>
       </c>
@@ -6238,7 +6239,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>19</v>
       </c>
@@ -6276,7 +6277,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6314,7 +6315,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F65" s="1" t="s">
         <v>93</v>
       </c>
@@ -6334,7 +6335,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F66" s="1" t="s">
         <v>121</v>
       </c>
@@ -6354,7 +6355,7 @@
         <v>527.5</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>19</v>
       </c>
@@ -6392,7 +6393,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>19</v>
       </c>
@@ -6430,7 +6431,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>19</v>
       </c>
@@ -6468,7 +6469,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>19</v>
       </c>
@@ -6506,7 +6507,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>19</v>
       </c>
@@ -6544,7 +6545,7 @@
         <v>26.2</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>19</v>
       </c>
@@ -6582,7 +6583,7 @@
         <v>25.9</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>19</v>
       </c>
@@ -6620,7 +6621,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>19</v>
       </c>
@@ -6658,7 +6659,7 @@
         <v>25.8</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>19</v>
       </c>
@@ -6696,7 +6697,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>19</v>
       </c>
@@ -6734,7 +6735,7 @@
         <v>28.8</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>19</v>
       </c>
@@ -6772,7 +6773,7 @@
         <v>26.4</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>19</v>
       </c>
@@ -6810,7 +6811,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>19</v>
       </c>
@@ -6848,7 +6849,7 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>19</v>
       </c>
@@ -6886,7 +6887,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>19</v>
       </c>
@@ -6924,7 +6925,7 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>19</v>
       </c>
@@ -6962,7 +6963,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>19</v>
       </c>
@@ -7000,7 +7001,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>19</v>
       </c>
@@ -7038,7 +7039,7 @@
         <v>25.4</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>19</v>
       </c>
@@ -7076,7 +7077,7 @@
         <v>26.2</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>19</v>
       </c>
@@ -7114,7 +7115,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>19</v>
       </c>
@@ -7152,7 +7153,7 @@
         <v>25.4</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>19</v>
       </c>
@@ -7190,7 +7191,7 @@
         <v>26.2</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>19</v>
       </c>
@@ -7228,7 +7229,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>19</v>
       </c>
@@ -7266,7 +7267,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>19</v>
       </c>
@@ -7304,7 +7305,7 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>19</v>
       </c>
@@ -7342,7 +7343,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>19</v>
       </c>
@@ -7380,7 +7381,7 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>19</v>
       </c>
@@ -7418,7 +7419,7 @@
         <v>26.2</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>19</v>
       </c>
@@ -7456,7 +7457,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>19</v>
       </c>
@@ -7494,7 +7495,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>19</v>
       </c>
@@ -7532,7 +7533,7 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>19</v>
       </c>
@@ -7570,7 +7571,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>19</v>
       </c>
@@ -7608,7 +7609,7 @@
         <v>26.4</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>19</v>
       </c>
@@ -7646,7 +7647,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>19</v>
       </c>
@@ -7684,7 +7685,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>19</v>
       </c>
@@ -7722,7 +7723,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>19</v>
       </c>
@@ -7760,7 +7761,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
         <v>19</v>
       </c>
@@ -7798,7 +7799,7 @@
         <v>26.9</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>19</v>
       </c>
@@ -7836,7 +7837,7 @@
         <v>25.8</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
         <v>19</v>
       </c>
@@ -7874,7 +7875,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
         <v>19</v>
       </c>
@@ -7912,7 +7913,7 @@
         <v>26.9</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>19</v>
       </c>
@@ -7950,7 +7951,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
         <v>19</v>
       </c>
@@ -7988,7 +7989,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>19</v>
       </c>
@@ -8026,7 +8027,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
         <v>19</v>
       </c>
@@ -8064,7 +8065,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
         <v>19</v>
       </c>
@@ -8102,7 +8103,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
         <v>19</v>
       </c>
@@ -8140,7 +8141,7 @@
         <v>25.9</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
         <v>19</v>
       </c>
@@ -8178,7 +8179,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
         <v>19</v>
       </c>
@@ -8216,7 +8217,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
         <v>19</v>
       </c>
@@ -8254,7 +8255,7 @@
         <v>26.2</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
         <v>19</v>
       </c>
@@ -8292,7 +8293,7 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
         <v>19</v>
       </c>
@@ -8330,7 +8331,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
         <v>19</v>
       </c>
@@ -8368,7 +8369,7 @@
         <v>26.2</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
         <v>19</v>
       </c>
@@ -8406,7 +8407,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
         <v>19</v>
       </c>
@@ -8444,7 +8445,7 @@
         <v>26.4</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
         <v>19</v>
       </c>
@@ -8482,7 +8483,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
         <v>19</v>
       </c>
@@ -8520,7 +8521,7 @@
         <v>26.2</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
         <v>19</v>
       </c>
@@ -8558,7 +8559,7 @@
         <v>26.2</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
         <v>19</v>
       </c>
@@ -8596,7 +8597,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
         <v>19</v>
       </c>
@@ -8634,7 +8635,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
         <v>19</v>
       </c>
@@ -8672,7 +8673,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
         <v>19</v>
       </c>
@@ -8710,7 +8711,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
         <v>19</v>
       </c>
@@ -8748,7 +8749,7 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
         <v>19</v>
       </c>
@@ -8786,7 +8787,7 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
         <v>19</v>
       </c>
@@ -8824,7 +8825,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
         <v>19</v>
       </c>
@@ -8862,7 +8863,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
         <v>19</v>
       </c>
@@ -8900,7 +8901,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
         <v>19</v>
       </c>
@@ -8938,7 +8939,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
         <v>19</v>
       </c>
@@ -8976,7 +8977,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
         <v>19</v>
       </c>
@@ -9014,7 +9015,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
         <v>19</v>
       </c>
@@ -9052,7 +9053,7 @@
         <v>25.9</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
         <v>19</v>
       </c>
@@ -9090,7 +9091,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
         <v>19</v>
       </c>
@@ -9128,7 +9129,7 @@
         <v>25.8</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
         <v>19</v>
       </c>
@@ -9166,7 +9167,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
         <v>19</v>
       </c>
@@ -9204,7 +9205,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
         <v>19</v>
       </c>
@@ -9242,7 +9243,7 @@
         <v>26.2</v>
       </c>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
         <v>19</v>
       </c>
@@ -9280,7 +9281,7 @@
         <v>25.8</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
         <v>19</v>
       </c>
@@ -9318,7 +9319,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
         <v>19</v>
       </c>
@@ -9356,7 +9357,7 @@
         <v>26.4</v>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
         <v>19</v>
       </c>
@@ -9394,7 +9395,7 @@
         <v>25.7</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
         <v>19</v>
       </c>
@@ -9432,7 +9433,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
         <v>19</v>
       </c>
@@ -9470,7 +9471,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
         <v>19</v>
       </c>
@@ -9508,7 +9509,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
         <v>19</v>
       </c>
@@ -9546,7 +9547,7 @@
         <v>25.9</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
         <v>19</v>
       </c>
@@ -9584,7 +9585,7 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
         <v>19</v>
       </c>
@@ -9622,7 +9623,7 @@
         <v>25.9</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
         <v>19</v>
       </c>
@@ -9660,7 +9661,7 @@
         <v>26.2</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
         <v>19</v>
       </c>
@@ -9698,7 +9699,7 @@
         <v>26.4</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
         <v>19</v>
       </c>
@@ -9736,7 +9737,7 @@
         <v>26.2</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
         <v>19</v>
       </c>
@@ -9774,7 +9775,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
         <v>19</v>
       </c>
@@ -9812,7 +9813,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
         <v>19</v>
       </c>
@@ -9850,7 +9851,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
         <v>19</v>
       </c>
@@ -9888,7 +9889,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
         <v>19</v>
       </c>
@@ -9926,7 +9927,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
         <v>19</v>
       </c>
@@ -9964,7 +9965,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
         <v>19</v>
       </c>
@@ -10002,7 +10003,7 @@
         <v>25.7</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
         <v>19</v>
       </c>
@@ -10040,7 +10041,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
         <v>19</v>
       </c>
@@ -10078,7 +10079,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
         <v>19</v>
       </c>
@@ -10116,7 +10117,7 @@
         <v>28.6</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
         <v>19</v>
       </c>
@@ -10154,7 +10155,7 @@
         <v>25.9</v>
       </c>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
         <v>19</v>
       </c>
@@ -10192,7 +10193,7 @@
         <v>25.9</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
         <v>19</v>
       </c>
@@ -10230,7 +10231,7 @@
         <v>25.9</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
         <v>19</v>
       </c>
@@ -10268,7 +10269,7 @@
         <v>25.9</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
         <v>19</v>
       </c>
@@ -10306,7 +10307,7 @@
         <v>26.4</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
         <v>19</v>
       </c>
@@ -10344,7 +10345,7 @@
         <v>25.7</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
         <v>19</v>
       </c>
@@ -10382,7 +10383,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
         <v>19</v>
       </c>
@@ -10420,7 +10421,7 @@
         <v>17.2</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
         <v>19</v>
       </c>
@@ -10458,7 +10459,7 @@
         <v>26.4</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
         <v>19</v>
       </c>
@@ -10496,7 +10497,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
         <v>19</v>
       </c>
@@ -10534,7 +10535,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="s">
         <v>19</v>
       </c>
@@ -10572,7 +10573,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
         <v>19</v>
       </c>
@@ -10610,7 +10611,7 @@
         <v>26.2</v>
       </c>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="s">
         <v>19</v>
       </c>
@@ -10648,7 +10649,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
         <v>19</v>
       </c>
@@ -10686,7 +10687,7 @@
         <v>26.4</v>
       </c>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A181" s="1" t="s">
         <v>19</v>
       </c>
@@ -10724,7 +10725,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
         <v>19</v>
       </c>
@@ -10762,7 +10763,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A183" s="1" t="s">
         <v>19</v>
       </c>
@@ -10800,7 +10801,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
         <v>19</v>
       </c>
@@ -10838,7 +10839,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A185" s="1" t="s">
         <v>19</v>
       </c>
@@ -10876,7 +10877,7 @@
         <v>26.4</v>
       </c>
     </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
         <v>19</v>
       </c>
@@ -10914,7 +10915,7 @@
         <v>25.9</v>
       </c>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F187" s="1" t="s">
         <v>93</v>
       </c>
@@ -10934,7 +10935,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F188" s="1" t="s">
         <v>331</v>
       </c>
@@ -10954,7 +10955,7 @@
         <v>3124.4</v>
       </c>
     </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A189" s="1" t="s">
         <v>19</v>
       </c>
@@ -10992,7 +10993,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="s">
         <v>19</v>
       </c>
@@ -11030,7 +11031,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A191" s="1" t="s">
         <v>19</v>
       </c>
@@ -11068,7 +11069,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
         <v>19</v>
       </c>
@@ -11106,7 +11107,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A193" s="1" t="s">
         <v>19</v>
       </c>
@@ -11144,7 +11145,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="s">
         <v>19</v>
       </c>
@@ -11182,7 +11183,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A195" s="1" t="s">
         <v>19</v>
       </c>
@@ -11220,7 +11221,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
         <v>19</v>
       </c>
@@ -11258,7 +11259,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A197" s="1" t="s">
         <v>19</v>
       </c>
@@ -11296,7 +11297,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A198" s="1" t="s">
         <v>19</v>
       </c>
@@ -11334,7 +11335,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A199" s="1" t="s">
         <v>19</v>
       </c>
@@ -11372,7 +11373,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
         <v>19</v>
       </c>
@@ -11410,7 +11411,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A201" s="1" t="s">
         <v>19</v>
       </c>
@@ -11448,7 +11449,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="s">
         <v>19</v>
       </c>
@@ -11486,7 +11487,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A203" s="1" t="s">
         <v>19</v>
       </c>
@@ -11524,7 +11525,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="s">
         <v>19</v>
       </c>
@@ -11562,7 +11563,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A205" s="1" t="s">
         <v>19</v>
       </c>
@@ -11600,7 +11601,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
         <v>19</v>
       </c>
@@ -11638,7 +11639,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A207" s="1" t="s">
         <v>19</v>
       </c>
@@ -11676,7 +11677,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="s">
         <v>19</v>
       </c>
@@ -11714,7 +11715,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A209" s="1" t="s">
         <v>19</v>
       </c>
@@ -11752,7 +11753,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="s">
         <v>19</v>
       </c>
@@ -11790,7 +11791,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A211" s="1" t="s">
         <v>19</v>
       </c>
@@ -11828,7 +11829,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A212" s="1" t="s">
         <v>19</v>
       </c>
@@ -11866,7 +11867,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A213" s="1" t="s">
         <v>19</v>
       </c>
@@ -11904,7 +11905,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
         <v>19</v>
       </c>
@@ -11942,7 +11943,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A215" s="1" t="s">
         <v>19</v>
       </c>
@@ -11980,7 +11981,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
         <v>19</v>
       </c>
@@ -12018,7 +12019,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A217" s="1" t="s">
         <v>19</v>
       </c>
@@ -12056,7 +12057,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
         <v>19</v>
       </c>
@@ -12094,7 +12095,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A219" s="1" t="s">
         <v>19</v>
       </c>
@@ -12132,7 +12133,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
         <v>19</v>
       </c>
@@ -12170,7 +12171,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A221" s="1" t="s">
         <v>19</v>
       </c>
@@ -12208,7 +12209,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A222" s="1" t="s">
         <v>19</v>
       </c>
@@ -12246,7 +12247,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F223" s="1" t="s">
         <v>93</v>
       </c>
@@ -12266,7 +12267,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F224" s="1" t="s">
         <v>95</v>
       </c>
@@ -12286,7 +12287,7 @@
         <v>808.8</v>
       </c>
     </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A225" s="1" t="s">
         <v>19</v>
       </c>
@@ -12324,7 +12325,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="s">
         <v>19</v>
       </c>
@@ -12362,7 +12363,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A227" s="1" t="s">
         <v>19</v>
       </c>
@@ -12400,7 +12401,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
         <v>19</v>
       </c>
@@ -12438,7 +12439,7 @@
         <v>29.4</v>
       </c>
     </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A229" s="1" t="s">
         <v>19</v>
       </c>
@@ -12476,7 +12477,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A230" s="1" t="s">
         <v>19</v>
       </c>
@@ -12514,7 +12515,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A231" s="1" t="s">
         <v>19</v>
       </c>
@@ -12552,7 +12553,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A232" s="1" t="s">
         <v>19</v>
       </c>
@@ -12590,7 +12591,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A233" s="1" t="s">
         <v>19</v>
       </c>
@@ -12628,7 +12629,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A234" s="1" t="s">
         <v>19</v>
       </c>
@@ -12666,7 +12667,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A235" s="1" t="s">
         <v>19</v>
       </c>
@@ -12704,7 +12705,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A236" s="1" t="s">
         <v>19</v>
       </c>
@@ -12742,7 +12743,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A237" s="1" t="s">
         <v>19</v>
       </c>
@@ -12780,7 +12781,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A238" s="1" t="s">
         <v>19</v>
       </c>
@@ -12818,7 +12819,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A239" s="1" t="s">
         <v>19</v>
       </c>
@@ -12856,7 +12857,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A240" s="1" t="s">
         <v>19</v>
       </c>
@@ -12894,7 +12895,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="241" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A241" s="1" t="s">
         <v>19</v>
       </c>
@@ -12932,7 +12933,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="242" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A242" s="1" t="s">
         <v>19</v>
       </c>
@@ -12970,7 +12971,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="243" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A243" s="1" t="s">
         <v>19</v>
       </c>
@@ -13008,7 +13009,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="244" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A244" s="1" t="s">
         <v>19</v>
       </c>
@@ -13046,7 +13047,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="245" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A245" s="1" t="s">
         <v>19</v>
       </c>
@@ -13084,7 +13085,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="246" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A246" s="1" t="s">
         <v>19</v>
       </c>
@@ -13122,7 +13123,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="247" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A247" s="1" t="s">
         <v>19</v>
       </c>
@@ -13160,7 +13161,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="248" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="s">
         <v>19</v>
       </c>
@@ -13198,7 +13199,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="249" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A249" s="1" t="s">
         <v>19</v>
       </c>
@@ -13236,7 +13237,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="250" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="s">
         <v>19</v>
       </c>
@@ -13274,7 +13275,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="251" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A251" s="1" t="s">
         <v>19</v>
       </c>
@@ -13312,7 +13313,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="252" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="s">
         <v>19</v>
       </c>
@@ -13350,7 +13351,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="253" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A253" s="1" t="s">
         <v>19</v>
       </c>
@@ -13388,7 +13389,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="254" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="s">
         <v>19</v>
       </c>
@@ -13426,7 +13427,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="255" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A255" s="1" t="s">
         <v>19</v>
       </c>
@@ -13464,7 +13465,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="256" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="s">
         <v>19</v>
       </c>
@@ -13502,7 +13503,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="257" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A257" s="1" t="s">
         <v>19</v>
       </c>
@@ -13540,7 +13541,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="258" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A258" s="1" t="s">
         <v>19</v>
       </c>
@@ -13578,7 +13579,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="259" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F259" s="1" t="s">
         <v>93</v>
       </c>
@@ -13598,7 +13599,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="260" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F260" s="1" t="s">
         <v>95</v>
       </c>
@@ -13618,7 +13619,7 @@
         <v>784.3</v>
       </c>
     </row>
-    <row r="261" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A261" s="1" t="s">
         <v>19</v>
       </c>
@@ -13656,7 +13657,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="262" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A262" s="1" t="s">
         <v>19</v>
       </c>
@@ -13694,7 +13695,7 @@
         <v>26.2</v>
       </c>
     </row>
-    <row r="263" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A263" s="1" t="s">
         <v>19</v>
       </c>
@@ -13732,7 +13733,7 @@
         <v>27.1</v>
       </c>
     </row>
-    <row r="264" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A264" s="1" t="s">
         <v>19</v>
       </c>
@@ -13770,7 +13771,7 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="265" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A265" s="1" t="s">
         <v>19</v>
       </c>
@@ -13808,7 +13809,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="266" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A266" s="1" t="s">
         <v>19</v>
       </c>
@@ -13846,7 +13847,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="267" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A267" s="1" t="s">
         <v>19</v>
       </c>
@@ -13884,7 +13885,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="268" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A268" s="1" t="s">
         <v>19</v>
       </c>
@@ -13922,7 +13923,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="269" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A269" s="1" t="s">
         <v>19</v>
       </c>
@@ -13960,7 +13961,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="270" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A270" s="1" t="s">
         <v>19</v>
       </c>
@@ -13998,7 +13999,7 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="271" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A271" s="1" t="s">
         <v>19</v>
       </c>
@@ -14036,7 +14037,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="272" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A272" s="1" t="s">
         <v>19</v>
       </c>
@@ -14074,7 +14075,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="273" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A273" s="1" t="s">
         <v>19</v>
       </c>
@@ -14112,7 +14113,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="274" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A274" s="1" t="s">
         <v>19</v>
       </c>
@@ -14150,7 +14151,7 @@
         <v>26.4</v>
       </c>
     </row>
-    <row r="275" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A275" s="1" t="s">
         <v>19</v>
       </c>
@@ -14188,7 +14189,7 @@
         <v>25.8</v>
       </c>
     </row>
-    <row r="276" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A276" s="1" t="s">
         <v>19</v>
       </c>
@@ -14226,7 +14227,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="277" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A277" s="1" t="s">
         <v>19</v>
       </c>
@@ -14264,7 +14265,7 @@
         <v>26.4</v>
       </c>
     </row>
-    <row r="278" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A278" s="1" t="s">
         <v>19</v>
       </c>
@@ -14302,7 +14303,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="279" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A279" s="1" t="s">
         <v>19</v>
       </c>
@@ -14340,7 +14341,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="280" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A280" s="1" t="s">
         <v>19</v>
       </c>
@@ -14378,7 +14379,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="281" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A281" s="1" t="s">
         <v>19</v>
       </c>
@@ -14416,7 +14417,7 @@
         <v>26.2</v>
       </c>
     </row>
-    <row r="282" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A282" s="1" t="s">
         <v>19</v>
       </c>
@@ -14454,7 +14455,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="283" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A283" s="1" t="s">
         <v>19</v>
       </c>
@@ -14492,7 +14493,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="284" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A284" s="1" t="s">
         <v>19</v>
       </c>
@@ -14530,7 +14531,7 @@
         <v>25.8</v>
       </c>
     </row>
-    <row r="285" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A285" s="1" t="s">
         <v>19</v>
       </c>
@@ -14568,7 +14569,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="286" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A286" s="1" t="s">
         <v>19</v>
       </c>
@@ -14606,7 +14607,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="287" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A287" s="1" t="s">
         <v>19</v>
       </c>
@@ -14644,7 +14645,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="288" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A288" s="1" t="s">
         <v>19</v>
       </c>
@@ -14682,7 +14683,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="289" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A289" s="1" t="s">
         <v>19</v>
       </c>
@@ -14720,7 +14721,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="290" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A290" s="1" t="s">
         <v>19</v>
       </c>
@@ -14758,7 +14759,7 @@
         <v>26.2</v>
       </c>
     </row>
-    <row r="291" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A291" s="1" t="s">
         <v>19</v>
       </c>
@@ -14796,7 +14797,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="292" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A292" s="1" t="s">
         <v>19</v>
       </c>
@@ -14834,7 +14835,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="293" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A293" s="1" t="s">
         <v>19</v>
       </c>
@@ -14872,7 +14873,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="294" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A294" s="1" t="s">
         <v>19</v>
       </c>
@@ -14910,7 +14911,7 @@
         <v>26.2</v>
       </c>
     </row>
-    <row r="295" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A295" s="1" t="s">
         <v>19</v>
       </c>
@@ -14948,7 +14949,7 @@
         <v>31.9</v>
       </c>
     </row>
-    <row r="296" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A296" s="1" t="s">
         <v>19</v>
       </c>
@@ -14986,7 +14987,7 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="297" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A297" s="1" t="s">
         <v>19</v>
       </c>
@@ -15024,7 +15025,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="298" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A298" s="1" t="s">
         <v>19</v>
       </c>
@@ -15062,7 +15063,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="299" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A299" s="1" t="s">
         <v>19</v>
       </c>
@@ -15100,7 +15101,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="300" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A300" s="1" t="s">
         <v>19</v>
       </c>
@@ -15138,7 +15139,7 @@
         <v>26.2</v>
       </c>
     </row>
-    <row r="301" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A301" s="1" t="s">
         <v>19</v>
       </c>
@@ -15176,7 +15177,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="302" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A302" s="1" t="s">
         <v>19</v>
       </c>
@@ -15214,7 +15215,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="303" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A303" s="1" t="s">
         <v>19</v>
       </c>
@@ -15252,7 +15253,7 @@
         <v>27.3</v>
       </c>
     </row>
-    <row r="304" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A304" s="1" t="s">
         <v>19</v>
       </c>
@@ -15290,7 +15291,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="305" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A305" s="1" t="s">
         <v>19</v>
       </c>
@@ -15328,7 +15329,7 @@
         <v>26.9</v>
       </c>
     </row>
-    <row r="306" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A306" s="1" t="s">
         <v>19</v>
       </c>
@@ -15366,7 +15367,7 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="307" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A307" s="1" t="s">
         <v>19</v>
       </c>
@@ -15404,7 +15405,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="308" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A308" s="1" t="s">
         <v>19</v>
       </c>
@@ -15442,7 +15443,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="309" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A309" s="1" t="s">
         <v>19</v>
       </c>
@@ -15480,7 +15481,7 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="310" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A310" s="1" t="s">
         <v>19</v>
       </c>
@@ -15518,7 +15519,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="311" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A311" s="1" t="s">
         <v>19</v>
       </c>
@@ -15556,7 +15557,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="312" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A312" s="1" t="s">
         <v>19</v>
       </c>
@@ -15594,7 +15595,7 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="313" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A313" s="1" t="s">
         <v>19</v>
       </c>
@@ -15632,7 +15633,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="314" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A314" s="1" t="s">
         <v>19</v>
       </c>
@@ -15670,7 +15671,7 @@
         <v>17.399999999999999</v>
       </c>
     </row>
-    <row r="315" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A315" s="1" t="s">
         <v>19</v>
       </c>
@@ -15708,7 +15709,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="316" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A316" s="1" t="s">
         <v>19</v>
       </c>
@@ -15746,7 +15747,7 @@
         <v>25.7</v>
       </c>
     </row>
-    <row r="317" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A317" s="1" t="s">
         <v>19</v>
       </c>
@@ -15784,7 +15785,7 @@
         <v>27.1</v>
       </c>
     </row>
-    <row r="318" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A318" s="1" t="s">
         <v>19</v>
       </c>
@@ -15822,7 +15823,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="319" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A319" s="1" t="s">
         <v>19</v>
       </c>
@@ -15860,7 +15861,7 @@
         <v>26.9</v>
       </c>
     </row>
-    <row r="320" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A320" s="1" t="s">
         <v>19</v>
       </c>
@@ -15898,7 +15899,7 @@
         <v>17.8</v>
       </c>
     </row>
-    <row r="321" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A321" s="1" t="s">
         <v>19</v>
       </c>
@@ -15936,7 +15937,7 @@
         <v>26.2</v>
       </c>
     </row>
-    <row r="322" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A322" s="1" t="s">
         <v>19</v>
       </c>
@@ -15974,7 +15975,7 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="323" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A323" s="1" t="s">
         <v>19</v>
       </c>
@@ -16012,7 +16013,7 @@
         <v>26.2</v>
       </c>
     </row>
-    <row r="324" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A324" s="1" t="s">
         <v>19</v>
       </c>
@@ -16050,7 +16051,7 @@
         <v>28.7</v>
       </c>
     </row>
-    <row r="325" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A325" s="1" t="s">
         <v>19</v>
       </c>
@@ -16088,7 +16089,7 @@
         <v>26.4</v>
       </c>
     </row>
-    <row r="326" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A326" s="1" t="s">
         <v>19</v>
       </c>
@@ -16126,7 +16127,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="327" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A327" s="1" t="s">
         <v>19</v>
       </c>
@@ -16164,7 +16165,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="328" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A328" s="1" t="s">
         <v>19</v>
       </c>
@@ -16202,7 +16203,7 @@
         <v>25.9</v>
       </c>
     </row>
-    <row r="329" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A329" s="1" t="s">
         <v>19</v>
       </c>
@@ -16240,7 +16241,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="330" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A330" s="1" t="s">
         <v>19</v>
       </c>
@@ -16278,7 +16279,7 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="331" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A331" s="1" t="s">
         <v>19</v>
       </c>
@@ -16316,7 +16317,7 @@
         <v>26.2</v>
       </c>
     </row>
-    <row r="332" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A332" s="1" t="s">
         <v>19</v>
       </c>
@@ -16354,7 +16355,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="333" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A333" s="1" t="s">
         <v>19</v>
       </c>
@@ -16392,7 +16393,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="334" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A334" s="1" t="s">
         <v>19</v>
       </c>
@@ -16430,7 +16431,7 @@
         <v>30.2</v>
       </c>
     </row>
-    <row r="335" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A335" s="1" t="s">
         <v>19</v>
       </c>
@@ -16468,7 +16469,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="336" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A336" s="1" t="s">
         <v>19</v>
       </c>
@@ -16506,7 +16507,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="337" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A337" s="1" t="s">
         <v>19</v>
       </c>
@@ -16544,7 +16545,7 @@
         <v>26.2</v>
       </c>
     </row>
-    <row r="338" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A338" s="1" t="s">
         <v>19</v>
       </c>
@@ -16582,7 +16583,7 @@
         <v>25.2</v>
       </c>
     </row>
-    <row r="339" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A339" s="1" t="s">
         <v>19</v>
       </c>
@@ -16620,7 +16621,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="340" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A340" s="1" t="s">
         <v>19</v>
       </c>
@@ -16658,7 +16659,7 @@
         <v>36.6</v>
       </c>
     </row>
-    <row r="341" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A341" s="1" t="s">
         <v>19</v>
       </c>
@@ -16696,7 +16697,7 @@
         <v>25.2</v>
       </c>
     </row>
-    <row r="342" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A342" s="1" t="s">
         <v>19</v>
       </c>
@@ -16734,7 +16735,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="343" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A343" s="1" t="s">
         <v>19</v>
       </c>
@@ -16772,7 +16773,7 @@
         <v>25.2</v>
       </c>
     </row>
-    <row r="344" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A344" s="1" t="s">
         <v>19</v>
       </c>
@@ -16810,7 +16811,7 @@
         <v>25.9</v>
       </c>
     </row>
-    <row r="345" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A345" s="1" t="s">
         <v>19</v>
       </c>
@@ -16848,7 +16849,7 @@
         <v>26.9</v>
       </c>
     </row>
-    <row r="346" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A346" s="1" t="s">
         <v>19</v>
       </c>
@@ -16886,7 +16887,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="347" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A347" s="1" t="s">
         <v>19</v>
       </c>
@@ -16924,7 +16925,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="348" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A348" s="1" t="s">
         <v>19</v>
       </c>
@@ -16962,7 +16963,7 @@
         <v>14.7</v>
       </c>
     </row>
-    <row r="349" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A349" s="1" t="s">
         <v>19</v>
       </c>
@@ -17000,7 +17001,7 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="350" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A350" s="1" t="s">
         <v>19</v>
       </c>
@@ -17038,7 +17039,7 @@
         <v>25.7</v>
       </c>
     </row>
-    <row r="351" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A351" s="1" t="s">
         <v>19</v>
       </c>
@@ -17076,7 +17077,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="352" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A352" s="1" t="s">
         <v>19</v>
       </c>
@@ -17114,7 +17115,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="353" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A353" s="1" t="s">
         <v>19</v>
       </c>
@@ -17152,7 +17153,7 @@
         <v>26.9</v>
       </c>
     </row>
-    <row r="354" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A354" s="1" t="s">
         <v>19</v>
       </c>
@@ -17190,7 +17191,7 @@
         <v>25.9</v>
       </c>
     </row>
-    <row r="355" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A355" s="1" t="s">
         <v>19</v>
       </c>
@@ -17228,7 +17229,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="356" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A356" s="1" t="s">
         <v>19</v>
       </c>
@@ -17266,7 +17267,7 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="357" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A357" s="1" t="s">
         <v>19</v>
       </c>
@@ -17304,7 +17305,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="358" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A358" s="1" t="s">
         <v>19</v>
       </c>
@@ -17342,7 +17343,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="359" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A359" s="1" t="s">
         <v>19</v>
       </c>
@@ -17380,7 +17381,7 @@
         <v>25.7</v>
       </c>
     </row>
-    <row r="360" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A360" s="1" t="s">
         <v>19</v>
       </c>
@@ -17418,7 +17419,7 @@
         <v>27.3</v>
       </c>
     </row>
-    <row r="361" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A361" s="1" t="s">
         <v>19</v>
       </c>
@@ -17456,7 +17457,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="362" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A362" s="1" t="s">
         <v>19</v>
       </c>
@@ -17494,7 +17495,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="363" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A363" s="1" t="s">
         <v>19</v>
       </c>
@@ -17532,7 +17533,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="364" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A364" s="1" t="s">
         <v>19</v>
       </c>
@@ -17570,7 +17571,7 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="365" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A365" s="1" t="s">
         <v>19</v>
       </c>
@@ -17608,7 +17609,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="366" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A366" s="1" t="s">
         <v>19</v>
       </c>
@@ -17646,7 +17647,7 @@
         <v>26.9</v>
       </c>
     </row>
-    <row r="367" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A367" s="1" t="s">
         <v>19</v>
       </c>
@@ -17684,7 +17685,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="368" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A368" s="1" t="s">
         <v>19</v>
       </c>
@@ -17722,7 +17723,7 @@
         <v>26.4</v>
       </c>
     </row>
-    <row r="369" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A369" s="1" t="s">
         <v>19</v>
       </c>
@@ -17760,7 +17761,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="370" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A370" s="1" t="s">
         <v>19</v>
       </c>
@@ -17798,7 +17799,7 @@
         <v>26.4</v>
       </c>
     </row>
-    <row r="371" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A371" s="1" t="s">
         <v>19</v>
       </c>
@@ -17836,7 +17837,7 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="372" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A372" s="1" t="s">
         <v>19</v>
       </c>
@@ -17874,7 +17875,7 @@
         <v>25.9</v>
       </c>
     </row>
-    <row r="373" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A373" s="1" t="s">
         <v>19</v>
       </c>
@@ -17912,7 +17913,7 @@
         <v>25.2</v>
       </c>
     </row>
-    <row r="374" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A374" s="1" t="s">
         <v>19</v>
       </c>
@@ -17950,7 +17951,7 @@
         <v>19.2</v>
       </c>
     </row>
-    <row r="375" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A375" s="1" t="s">
         <v>19</v>
       </c>
@@ -17988,7 +17989,7 @@
         <v>27.1</v>
       </c>
     </row>
-    <row r="376" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A376" s="1" t="s">
         <v>19</v>
       </c>
@@ -18026,7 +18027,7 @@
         <v>26.9</v>
       </c>
     </row>
-    <row r="377" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A377" s="1" t="s">
         <v>19</v>
       </c>
@@ -18064,7 +18065,7 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="378" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A378" s="1" t="s">
         <v>19</v>
       </c>
@@ -18102,7 +18103,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="379" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A379" s="1" t="s">
         <v>19</v>
       </c>
@@ -18140,7 +18141,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="380" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F380" s="1" t="s">
         <v>93</v>
       </c>
@@ -18160,7 +18161,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="381" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F381" s="1" t="s">
         <v>528</v>
       </c>
@@ -18180,7 +18181,7 @@
         <v>3060</v>
       </c>
     </row>
-    <row r="382" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A382" s="1" t="s">
         <v>19</v>
       </c>
@@ -18218,7 +18219,7 @@
         <v>25.2</v>
       </c>
     </row>
-    <row r="383" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A383" s="1" t="s">
         <v>19</v>
       </c>
@@ -18256,7 +18257,7 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="384" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A384" s="1" t="s">
         <v>19</v>
       </c>
@@ -18294,7 +18295,7 @@
         <v>26.2</v>
       </c>
     </row>
-    <row r="385" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A385" s="1" t="s">
         <v>19</v>
       </c>
@@ -18332,7 +18333,7 @@
         <v>25.9</v>
       </c>
     </row>
-    <row r="386" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A386" s="1" t="s">
         <v>19</v>
       </c>
@@ -18370,7 +18371,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="387" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A387" s="1" t="s">
         <v>19</v>
       </c>
@@ -18408,7 +18409,7 @@
         <v>25.8</v>
       </c>
     </row>
-    <row r="388" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A388" s="1" t="s">
         <v>19</v>
       </c>
@@ -18446,7 +18447,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="389" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A389" s="1" t="s">
         <v>19</v>
       </c>
@@ -18484,7 +18485,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="390" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A390" s="1" t="s">
         <v>19</v>
       </c>
@@ -18522,7 +18523,7 @@
         <v>25.8</v>
       </c>
     </row>
-    <row r="391" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A391" s="1" t="s">
         <v>19</v>
       </c>
@@ -18560,7 +18561,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="392" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A392" s="1" t="s">
         <v>19</v>
       </c>
@@ -18598,7 +18599,7 @@
         <v>25.9</v>
       </c>
     </row>
-    <row r="393" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A393" s="1" t="s">
         <v>19</v>
       </c>
@@ -18636,7 +18637,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="394" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A394" s="1" t="s">
         <v>19</v>
       </c>
@@ -18674,7 +18675,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="395" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A395" s="1" t="s">
         <v>19</v>
       </c>
@@ -18712,7 +18713,7 @@
         <v>25.7</v>
       </c>
     </row>
-    <row r="396" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A396" s="1" t="s">
         <v>19</v>
       </c>
@@ -18750,7 +18751,7 @@
         <v>25.7</v>
       </c>
     </row>
-    <row r="397" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A397" s="1" t="s">
         <v>19</v>
       </c>
@@ -18788,7 +18789,7 @@
         <v>25.7</v>
       </c>
     </row>
-    <row r="398" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A398" s="1" t="s">
         <v>19</v>
       </c>
@@ -18826,7 +18827,7 @@
         <v>26.2</v>
       </c>
     </row>
-    <row r="399" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A399" s="1" t="s">
         <v>19</v>
       </c>
@@ -18864,7 +18865,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="400" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A400" s="1" t="s">
         <v>19</v>
       </c>
@@ -18902,7 +18903,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="401" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A401" s="1" t="s">
         <v>19</v>
       </c>
@@ -18940,7 +18941,7 @@
         <v>25.7</v>
       </c>
     </row>
-    <row r="402" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A402" s="1" t="s">
         <v>19</v>
       </c>
@@ -18978,7 +18979,7 @@
         <v>25.8</v>
       </c>
     </row>
-    <row r="403" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A403" s="1" t="s">
         <v>19</v>
       </c>
@@ -19016,7 +19017,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="404" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A404" s="1" t="s">
         <v>19</v>
       </c>
@@ -19054,7 +19055,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="405" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A405" s="1" t="s">
         <v>19</v>
       </c>
@@ -19092,7 +19093,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="406" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A406" s="1" t="s">
         <v>19</v>
       </c>
@@ -19130,7 +19131,7 @@
         <v>32.200000000000003</v>
       </c>
     </row>
-    <row r="407" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A407" s="1" t="s">
         <v>19</v>
       </c>
@@ -19168,7 +19169,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="408" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A408" s="1" t="s">
         <v>19</v>
       </c>
@@ -19206,7 +19207,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="409" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A409" s="1" t="s">
         <v>19</v>
       </c>
@@ -19244,7 +19245,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="410" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A410" s="1" t="s">
         <v>19</v>
       </c>
@@ -19282,7 +19283,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="411" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A411" s="1" t="s">
         <v>19</v>
       </c>
@@ -19320,7 +19321,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="412" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A412" s="1" t="s">
         <v>19</v>
       </c>
@@ -19358,7 +19359,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="413" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A413" s="1" t="s">
         <v>19</v>
       </c>
@@ -19396,7 +19397,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="414" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A414" s="1" t="s">
         <v>19</v>
       </c>
@@ -19434,7 +19435,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="415" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A415" s="1" t="s">
         <v>19</v>
       </c>
@@ -19472,7 +19473,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="416" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A416" s="1" t="s">
         <v>19</v>
       </c>
@@ -19510,7 +19511,7 @@
         <v>25.8</v>
       </c>
     </row>
-    <row r="417" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A417" s="1" t="s">
         <v>19</v>
       </c>
@@ -19548,7 +19549,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="418" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A418" s="1" t="s">
         <v>19</v>
       </c>
@@ -19586,7 +19587,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="419" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A419" s="1" t="s">
         <v>19</v>
       </c>
@@ -19624,7 +19625,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="420" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A420" s="1" t="s">
         <v>19</v>
       </c>
@@ -19662,7 +19663,7 @@
         <v>29.4</v>
       </c>
     </row>
-    <row r="421" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A421" s="1" t="s">
         <v>19</v>
       </c>
@@ -19700,7 +19701,7 @@
         <v>26.2</v>
       </c>
     </row>
-    <row r="422" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A422" s="1" t="s">
         <v>19</v>
       </c>
@@ -19738,7 +19739,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="423" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A423" s="1" t="s">
         <v>19</v>
       </c>
@@ -19776,7 +19777,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="424" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A424" s="1" t="s">
         <v>19</v>
       </c>
@@ -19814,7 +19815,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="425" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A425" s="1" t="s">
         <v>19</v>
       </c>
@@ -19852,7 +19853,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="426" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A426" s="1" t="s">
         <v>19</v>
       </c>
@@ -19890,7 +19891,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="427" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A427" s="1" t="s">
         <v>19</v>
       </c>
@@ -19928,7 +19929,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="428" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A428" s="1" t="s">
         <v>19</v>
       </c>
@@ -19966,7 +19967,7 @@
         <v>25.8</v>
       </c>
     </row>
-    <row r="429" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A429" s="1" t="s">
         <v>19</v>
       </c>
@@ -20004,7 +20005,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="430" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A430" s="1" t="s">
         <v>19</v>
       </c>
@@ -20042,7 +20043,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="431" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A431" s="1" t="s">
         <v>19</v>
       </c>
@@ -20080,7 +20081,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="432" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A432" s="1" t="s">
         <v>19</v>
       </c>
@@ -20118,7 +20119,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="433" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A433" s="1" t="s">
         <v>19</v>
       </c>
@@ -20156,7 +20157,7 @@
         <v>25.8</v>
       </c>
     </row>
-    <row r="434" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A434" s="1" t="s">
         <v>19</v>
       </c>
@@ -20194,7 +20195,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="435" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A435" s="1" t="s">
         <v>19</v>
       </c>
@@ -20232,7 +20233,7 @@
         <v>25.9</v>
       </c>
     </row>
-    <row r="436" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A436" s="1" t="s">
         <v>19</v>
       </c>
@@ -20270,7 +20271,7 @@
         <v>25.9</v>
       </c>
     </row>
-    <row r="437" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A437" s="1" t="s">
         <v>19</v>
       </c>
@@ -20308,7 +20309,7 @@
         <v>25.9</v>
       </c>
     </row>
-    <row r="438" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A438" s="1" t="s">
         <v>19</v>
       </c>
@@ -20346,7 +20347,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="439" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A439" s="1" t="s">
         <v>19</v>
       </c>
@@ -20384,7 +20385,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="440" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A440" s="1" t="s">
         <v>19</v>
       </c>
@@ -20422,7 +20423,7 @@
         <v>25.9</v>
       </c>
     </row>
-    <row r="441" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A441" s="1" t="s">
         <v>19</v>
       </c>
@@ -20460,7 +20461,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="442" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F442" s="1" t="s">
         <v>93</v>
       </c>
@@ -20480,7 +20481,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="443" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F443" s="1" t="s">
         <v>592</v>
       </c>
@@ -20500,7 +20501,7 @@
         <v>1503.3</v>
       </c>
     </row>
-    <row r="444" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A444" s="1" t="s">
         <v>19</v>
       </c>
@@ -20538,7 +20539,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="445" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A445" s="1" t="s">
         <v>19</v>
       </c>
@@ -20576,7 +20577,7 @@
         <v>27.9</v>
       </c>
     </row>
-    <row r="446" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A446" s="1" t="s">
         <v>19</v>
       </c>
@@ -20614,7 +20615,7 @@
         <v>28.4</v>
       </c>
     </row>
-    <row r="447" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A447" s="1" t="s">
         <v>19</v>
       </c>
@@ -20652,7 +20653,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="448" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A448" s="1" t="s">
         <v>19</v>
       </c>
@@ -20690,7 +20691,7 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="449" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A449" s="1" t="s">
         <v>19</v>
       </c>
@@ -20728,7 +20729,7 @@
         <v>27.8</v>
       </c>
     </row>
-    <row r="450" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A450" s="1" t="s">
         <v>19</v>
       </c>
@@ -20766,7 +20767,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="451" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A451" s="1" t="s">
         <v>19</v>
       </c>
@@ -20804,7 +20805,7 @@
         <v>28.5</v>
       </c>
     </row>
-    <row r="452" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A452" s="1" t="s">
         <v>19</v>
       </c>
@@ -20842,7 +20843,7 @@
         <v>27.8</v>
       </c>
     </row>
-    <row r="453" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A453" s="1" t="s">
         <v>19</v>
       </c>
@@ -20880,7 +20881,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="454" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A454" s="1" t="s">
         <v>19</v>
       </c>
@@ -20918,7 +20919,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="455" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A455" s="1" t="s">
         <v>19</v>
       </c>
@@ -20956,7 +20957,7 @@
         <v>19.399999999999999</v>
       </c>
     </row>
-    <row r="456" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A456" s="1" t="s">
         <v>19</v>
       </c>
@@ -20994,7 +20995,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="457" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A457" s="1" t="s">
         <v>19</v>
       </c>
@@ -21032,7 +21033,7 @@
         <v>28.5</v>
       </c>
     </row>
-    <row r="458" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A458" s="1" t="s">
         <v>19</v>
       </c>
@@ -21070,7 +21071,7 @@
         <v>27.3</v>
       </c>
     </row>
-    <row r="459" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A459" s="1" t="s">
         <v>19</v>
       </c>
@@ -21108,7 +21109,7 @@
         <v>26.9</v>
       </c>
     </row>
-    <row r="460" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A460" s="1" t="s">
         <v>19</v>
       </c>
@@ -21146,7 +21147,7 @@
         <v>27.7</v>
       </c>
     </row>
-    <row r="461" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A461" s="1" t="s">
         <v>19</v>
       </c>
@@ -21184,7 +21185,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="462" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A462" s="1" t="s">
         <v>19</v>
       </c>
@@ -21222,7 +21223,7 @@
         <v>27.2</v>
       </c>
     </row>
-    <row r="463" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A463" s="1" t="s">
         <v>19</v>
       </c>
@@ -21260,7 +21261,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="464" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A464" s="1" t="s">
         <v>19</v>
       </c>
@@ -21298,7 +21299,7 @@
         <v>27.4</v>
       </c>
     </row>
-    <row r="465" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A465" s="1" t="s">
         <v>19</v>
       </c>
@@ -21336,7 +21337,7 @@
         <v>28.1</v>
       </c>
     </row>
-    <row r="466" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A466" s="1" t="s">
         <v>19</v>
       </c>
@@ -21374,7 +21375,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="467" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A467" s="1" t="s">
         <v>19</v>
       </c>
@@ -21412,7 +21413,7 @@
         <v>28.1</v>
       </c>
     </row>
-    <row r="468" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A468" s="1" t="s">
         <v>19</v>
       </c>
@@ -21450,7 +21451,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="469" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A469" s="1" t="s">
         <v>19</v>
       </c>
@@ -21488,7 +21489,7 @@
         <v>27.8</v>
       </c>
     </row>
-    <row r="470" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A470" s="1" t="s">
         <v>19</v>
       </c>
@@ -21526,7 +21527,7 @@
         <v>27.7</v>
       </c>
     </row>
-    <row r="471" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A471" s="1" t="s">
         <v>19</v>
       </c>
@@ -21564,7 +21565,7 @@
         <v>27.9</v>
       </c>
     </row>
-    <row r="472" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A472" s="1" t="s">
         <v>19</v>
       </c>
@@ -21602,7 +21603,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="473" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A473" s="1" t="s">
         <v>19</v>
       </c>
@@ -21640,7 +21641,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="474" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A474" s="1" t="s">
         <v>19</v>
       </c>
@@ -21678,7 +21679,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="475" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A475" s="1" t="s">
         <v>19</v>
       </c>
@@ -21716,7 +21717,7 @@
         <v>27.8</v>
       </c>
     </row>
-    <row r="476" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A476" s="1" t="s">
         <v>19</v>
       </c>
@@ -21754,7 +21755,7 @@
         <v>14.1</v>
       </c>
     </row>
-    <row r="477" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A477" s="1" t="s">
         <v>19</v>
       </c>
@@ -21792,7 +21793,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="478" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A478" s="1" t="s">
         <v>19</v>
       </c>
@@ -21830,7 +21831,7 @@
         <v>27.8</v>
       </c>
     </row>
-    <row r="479" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A479" s="1" t="s">
         <v>19</v>
       </c>
@@ -21868,7 +21869,7 @@
         <v>28.3</v>
       </c>
     </row>
-    <row r="480" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A480" s="1" t="s">
         <v>19</v>
       </c>
@@ -21906,7 +21907,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="481" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A481" s="1" t="s">
         <v>19</v>
       </c>
@@ -21944,7 +21945,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="482" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A482" s="1" t="s">
         <v>19</v>
       </c>
@@ -21982,7 +21983,7 @@
         <v>27.8</v>
       </c>
     </row>
-    <row r="483" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A483" s="1" t="s">
         <v>19</v>
       </c>
@@ -22020,7 +22021,7 @@
         <v>27.9</v>
       </c>
     </row>
-    <row r="484" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A484" s="1" t="s">
         <v>19</v>
       </c>
@@ -22058,7 +22059,7 @@
         <v>28.2</v>
       </c>
     </row>
-    <row r="485" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A485" s="1" t="s">
         <v>19</v>
       </c>
@@ -22096,7 +22097,7 @@
         <v>28.5</v>
       </c>
     </row>
-    <row r="486" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A486" s="1" t="s">
         <v>19</v>
       </c>
@@ -22134,7 +22135,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="487" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A487" s="1" t="s">
         <v>19</v>
       </c>
@@ -22172,7 +22173,7 @@
         <v>27.9</v>
       </c>
     </row>
-    <row r="488" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A488" s="1" t="s">
         <v>19</v>
       </c>
@@ -22210,7 +22211,7 @@
         <v>28.1</v>
       </c>
     </row>
-    <row r="489" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A489" s="1" t="s">
         <v>19</v>
       </c>
@@ -22248,7 +22249,7 @@
         <v>27.9</v>
       </c>
     </row>
-    <row r="490" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A490" s="1" t="s">
         <v>19</v>
       </c>
@@ -22286,7 +22287,7 @@
         <v>27.1</v>
       </c>
     </row>
-    <row r="491" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A491" s="1" t="s">
         <v>19</v>
       </c>
@@ -22324,7 +22325,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="492" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A492" s="1" t="s">
         <v>19</v>
       </c>
@@ -22362,7 +22363,7 @@
         <v>27.8</v>
       </c>
     </row>
-    <row r="493" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A493" s="1" t="s">
         <v>19</v>
       </c>
@@ -22400,7 +22401,7 @@
         <v>27.9</v>
       </c>
     </row>
-    <row r="494" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A494" s="1" t="s">
         <v>19</v>
       </c>
@@ -22438,7 +22439,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="495" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A495" s="1" t="s">
         <v>19</v>
       </c>
@@ -22476,7 +22477,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="496" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A496" s="1" t="s">
         <v>19</v>
       </c>
@@ -22514,7 +22515,7 @@
         <v>27.7</v>
       </c>
     </row>
-    <row r="497" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A497" s="1" t="s">
         <v>19</v>
       </c>
@@ -22552,7 +22553,7 @@
         <v>26.2</v>
       </c>
     </row>
-    <row r="498" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A498" s="1" t="s">
         <v>19</v>
       </c>
@@ -22590,7 +22591,7 @@
         <v>29.7</v>
       </c>
     </row>
-    <row r="499" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A499" s="1" t="s">
         <v>19</v>
       </c>
@@ -22628,7 +22629,7 @@
         <v>26.2</v>
       </c>
     </row>
-    <row r="500" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A500" s="1" t="s">
         <v>19</v>
       </c>
@@ -22666,7 +22667,7 @@
         <v>29.4</v>
       </c>
     </row>
-    <row r="501" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A501" s="1" t="s">
         <v>19</v>
       </c>
@@ -22704,7 +22705,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="502" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A502" s="1" t="s">
         <v>19</v>
       </c>
@@ -22742,7 +22743,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="503" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A503" s="1" t="s">
         <v>19</v>
       </c>
@@ -22780,7 +22781,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="504" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A504" s="1" t="s">
         <v>19</v>
       </c>
@@ -22818,7 +22819,7 @@
         <v>29.2</v>
       </c>
     </row>
-    <row r="505" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A505" s="1" t="s">
         <v>19</v>
       </c>
@@ -22856,7 +22857,7 @@
         <v>28.1</v>
       </c>
     </row>
-    <row r="506" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A506" s="1" t="s">
         <v>19</v>
       </c>
@@ -22894,7 +22895,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="507" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A507" s="1" t="s">
         <v>19</v>
       </c>
@@ -22932,7 +22933,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="508" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A508" s="1" t="s">
         <v>19</v>
       </c>
@@ -22970,7 +22971,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="509" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A509" s="1" t="s">
         <v>19</v>
       </c>
@@ -23008,7 +23009,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="510" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A510" s="1" t="s">
         <v>19</v>
       </c>
@@ -23046,7 +23047,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="511" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A511" s="1" t="s">
         <v>19</v>
       </c>
@@ -23084,7 +23085,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="512" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A512" s="1" t="s">
         <v>19</v>
       </c>
@@ -23122,7 +23123,7 @@
         <v>27.1</v>
       </c>
     </row>
-    <row r="513" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A513" s="1" t="s">
         <v>19</v>
       </c>
@@ -23160,7 +23161,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="514" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A514" s="1" t="s">
         <v>19</v>
       </c>
@@ -23198,7 +23199,7 @@
         <v>27.2</v>
       </c>
     </row>
-    <row r="515" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A515" s="1" t="s">
         <v>19</v>
       </c>
@@ -23236,7 +23237,7 @@
         <v>28.1</v>
       </c>
     </row>
-    <row r="516" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A516" s="1" t="s">
         <v>19</v>
       </c>
@@ -23274,7 +23275,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="517" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A517" s="1" t="s">
         <v>19</v>
       </c>
@@ -23312,7 +23313,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="518" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A518" s="1" t="s">
         <v>19</v>
       </c>
@@ -23350,7 +23351,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="519" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A519" s="1" t="s">
         <v>19</v>
       </c>
@@ -23388,7 +23389,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="520" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A520" s="1" t="s">
         <v>19</v>
       </c>
@@ -23426,7 +23427,7 @@
         <v>25.2</v>
       </c>
     </row>
-    <row r="521" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A521" s="1" t="s">
         <v>19</v>
       </c>
@@ -23464,7 +23465,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="522" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A522" s="1" t="s">
         <v>19</v>
       </c>
@@ -23502,7 +23503,7 @@
         <v>27.9</v>
       </c>
     </row>
-    <row r="523" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A523" s="1" t="s">
         <v>19</v>
       </c>
@@ -23540,7 +23541,7 @@
         <v>27.7</v>
       </c>
     </row>
-    <row r="524" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A524" s="1" t="s">
         <v>19</v>
       </c>
@@ -23578,7 +23579,7 @@
         <v>25.2</v>
       </c>
     </row>
-    <row r="525" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A525" s="1" t="s">
         <v>19</v>
       </c>
@@ -23616,7 +23617,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="526" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A526" s="1" t="s">
         <v>19</v>
       </c>
@@ -23654,7 +23655,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="527" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A527" s="1" t="s">
         <v>19</v>
       </c>
@@ -23692,7 +23693,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="528" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A528" s="1" t="s">
         <v>19</v>
       </c>
@@ -23730,7 +23731,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="529" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A529" s="1" t="s">
         <v>19</v>
       </c>
@@ -23768,7 +23769,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="530" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A530" s="1" t="s">
         <v>19</v>
       </c>
@@ -23806,7 +23807,7 @@
         <v>28.2</v>
       </c>
     </row>
-    <row r="531" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A531" s="1" t="s">
         <v>19</v>
       </c>
@@ -23844,7 +23845,7 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="532" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A532" s="1" t="s">
         <v>19</v>
       </c>
@@ -23882,7 +23883,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="533" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A533" s="1" t="s">
         <v>19</v>
       </c>
@@ -23920,7 +23921,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="534" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A534" s="1" t="s">
         <v>19</v>
       </c>
@@ -23958,7 +23959,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="535" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A535" s="1" t="s">
         <v>19</v>
       </c>
@@ -23996,7 +23997,7 @@
         <v>25.4</v>
       </c>
     </row>
-    <row r="536" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A536" s="1" t="s">
         <v>19</v>
       </c>
@@ -24034,7 +24035,7 @@
         <v>25.2</v>
       </c>
     </row>
-    <row r="537" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A537" s="1" t="s">
         <v>19</v>
       </c>
@@ -24072,7 +24073,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="538" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A538" s="1" t="s">
         <v>19</v>
       </c>
@@ -24110,7 +24111,7 @@
         <v>28.3</v>
       </c>
     </row>
-    <row r="539" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A539" s="1" t="s">
         <v>19</v>
       </c>
@@ -24148,7 +24149,7 @@
         <v>25.7</v>
       </c>
     </row>
-    <row r="540" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A540" s="1" t="s">
         <v>19</v>
       </c>
@@ -24186,7 +24187,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="541" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A541" s="1" t="s">
         <v>19</v>
       </c>
@@ -24224,7 +24225,7 @@
         <v>25.2</v>
       </c>
     </row>
-    <row r="542" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A542" s="1" t="s">
         <v>19</v>
       </c>
@@ -24262,7 +24263,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="543" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A543" s="1" t="s">
         <v>19</v>
       </c>
@@ -24300,7 +24301,7 @@
         <v>29.2</v>
       </c>
     </row>
-    <row r="544" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A544" s="1" t="s">
         <v>19</v>
       </c>
@@ -24338,7 +24339,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="545" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A545" s="1" t="s">
         <v>19</v>
       </c>
@@ -24376,7 +24377,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="546" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A546" s="1" t="s">
         <v>19</v>
       </c>
@@ -24414,7 +24415,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="547" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A547" s="1" t="s">
         <v>19</v>
       </c>
@@ -24452,7 +24453,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="548" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A548" s="1" t="s">
         <v>19</v>
       </c>
@@ -24490,7 +24491,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="549" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A549" s="1" t="s">
         <v>19</v>
       </c>
@@ -24528,7 +24529,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="550" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A550" s="1" t="s">
         <v>19</v>
       </c>
@@ -24566,7 +24567,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="551" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A551" s="1" t="s">
         <v>19</v>
       </c>
@@ -24604,7 +24605,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="552" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A552" s="1" t="s">
         <v>19</v>
       </c>
@@ -24642,7 +24643,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="553" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A553" s="1" t="s">
         <v>19</v>
       </c>
@@ -24680,7 +24681,7 @@
         <v>27.4</v>
       </c>
     </row>
-    <row r="554" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A554" s="1" t="s">
         <v>19</v>
       </c>
@@ -24718,7 +24719,7 @@
         <v>27.1</v>
       </c>
     </row>
-    <row r="555" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A555" s="1" t="s">
         <v>19</v>
       </c>
@@ -24756,7 +24757,7 @@
         <v>27.4</v>
       </c>
     </row>
-    <row r="556" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A556" s="1" t="s">
         <v>19</v>
       </c>
@@ -24794,7 +24795,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="557" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A557" s="1" t="s">
         <v>19</v>
       </c>
@@ -24832,7 +24833,7 @@
         <v>28.6</v>
       </c>
     </row>
-    <row r="558" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A558" s="1" t="s">
         <v>19</v>
       </c>
@@ -24870,7 +24871,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="559" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A559" s="1" t="s">
         <v>19</v>
       </c>
@@ -24908,7 +24909,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="560" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A560" s="1" t="s">
         <v>19</v>
       </c>
@@ -24946,7 +24947,7 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="561" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A561" s="1" t="s">
         <v>19</v>
       </c>
@@ -24984,7 +24985,7 @@
         <v>28.1</v>
       </c>
     </row>
-    <row r="562" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A562" s="1" t="s">
         <v>19</v>
       </c>
@@ -25022,7 +25023,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="563" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A563" s="1" t="s">
         <v>19</v>
       </c>
@@ -25060,7 +25061,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="564" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A564" s="1" t="s">
         <v>19</v>
       </c>
@@ -25098,7 +25099,7 @@
         <v>28.5</v>
       </c>
     </row>
-    <row r="565" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A565" s="1" t="s">
         <v>19</v>
       </c>
@@ -25136,7 +25137,7 @@
         <v>27.4</v>
       </c>
     </row>
-    <row r="566" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A566" s="1" t="s">
         <v>19</v>
       </c>
@@ -25174,7 +25175,7 @@
         <v>27.3</v>
       </c>
     </row>
-    <row r="567" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A567" s="1" t="s">
         <v>19</v>
       </c>
@@ -25212,7 +25213,7 @@
         <v>27.8</v>
       </c>
     </row>
-    <row r="568" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A568" s="1" t="s">
         <v>19</v>
       </c>
@@ -25250,7 +25251,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="569" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A569" s="1" t="s">
         <v>19</v>
       </c>
@@ -25288,7 +25289,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="570" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A570" s="1" t="s">
         <v>19</v>
       </c>
@@ -25326,7 +25327,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="571" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A571" s="1" t="s">
         <v>19</v>
       </c>
@@ -25364,7 +25365,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="572" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A572" s="1" t="s">
         <v>19</v>
       </c>
@@ -25402,7 +25403,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="573" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A573" s="1" t="s">
         <v>19</v>
       </c>
@@ -25440,7 +25441,7 @@
         <v>27.4</v>
       </c>
     </row>
-    <row r="574" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A574" s="1" t="s">
         <v>19</v>
       </c>
@@ -25478,7 +25479,7 @@
         <v>27.9</v>
       </c>
     </row>
-    <row r="575" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A575" s="1" t="s">
         <v>19</v>
       </c>
@@ -25516,7 +25517,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="576" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A576" s="1" t="s">
         <v>19</v>
       </c>
@@ -25554,7 +25555,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="577" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A577" s="1" t="s">
         <v>19</v>
       </c>
@@ -25592,7 +25593,7 @@
         <v>27.8</v>
       </c>
     </row>
-    <row r="578" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A578" s="1" t="s">
         <v>19</v>
       </c>
@@ -25630,7 +25631,7 @@
         <v>27.7</v>
       </c>
     </row>
-    <row r="579" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A579" s="1" t="s">
         <v>19</v>
       </c>
@@ -25668,7 +25669,7 @@
         <v>27.7</v>
       </c>
     </row>
-    <row r="580" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A580" s="1" t="s">
         <v>19</v>
       </c>
@@ -25706,7 +25707,7 @@
         <v>27.1</v>
       </c>
     </row>
-    <row r="581" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A581" s="1" t="s">
         <v>19</v>
       </c>
@@ -25744,7 +25745,7 @@
         <v>27.9</v>
       </c>
     </row>
-    <row r="582" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A582" s="1" t="s">
         <v>19</v>
       </c>
@@ -25782,7 +25783,7 @@
         <v>27.2</v>
       </c>
     </row>
-    <row r="583" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A583" s="1" t="s">
         <v>19</v>
       </c>
@@ -25820,7 +25821,7 @@
         <v>27.8</v>
       </c>
     </row>
-    <row r="584" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A584" s="1" t="s">
         <v>19</v>
       </c>
@@ -25858,7 +25859,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="585" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A585" s="1" t="s">
         <v>19</v>
       </c>
@@ -25896,7 +25897,7 @@
         <v>27.2</v>
       </c>
     </row>
-    <row r="586" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A586" s="1" t="s">
         <v>19</v>
       </c>
@@ -25934,7 +25935,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="587" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A587" s="1" t="s">
         <v>19</v>
       </c>
@@ -25972,7 +25973,7 @@
         <v>27.8</v>
       </c>
     </row>
-    <row r="588" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A588" s="1" t="s">
         <v>19</v>
       </c>
@@ -26010,7 +26011,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="589" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A589" s="1" t="s">
         <v>19</v>
       </c>
@@ -26048,7 +26049,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="590" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A590" s="1" t="s">
         <v>19</v>
       </c>
@@ -26086,7 +26087,7 @@
         <v>27.4</v>
       </c>
     </row>
-    <row r="591" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A591" s="1" t="s">
         <v>19</v>
       </c>
@@ -26124,7 +26125,7 @@
         <v>27.7</v>
       </c>
     </row>
-    <row r="592" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A592" s="1" t="s">
         <v>19</v>
       </c>
@@ -26162,7 +26163,7 @@
         <v>26.9</v>
       </c>
     </row>
-    <row r="593" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A593" s="1" t="s">
         <v>19</v>
       </c>
@@ -26200,7 +26201,7 @@
         <v>27.2</v>
       </c>
     </row>
-    <row r="594" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A594" s="1" t="s">
         <v>19</v>
       </c>
@@ -26238,7 +26239,7 @@
         <v>27.4</v>
       </c>
     </row>
-    <row r="595" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A595" s="1" t="s">
         <v>19</v>
       </c>
@@ -26276,7 +26277,7 @@
         <v>27.8</v>
       </c>
     </row>
-    <row r="596" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A596" s="1" t="s">
         <v>19</v>
       </c>
@@ -26314,7 +26315,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="597" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A597" s="1" t="s">
         <v>19</v>
       </c>
@@ -26352,7 +26353,7 @@
         <v>28.1</v>
       </c>
     </row>
-    <row r="598" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A598" s="1" t="s">
         <v>19</v>
       </c>
@@ -26390,7 +26391,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="599" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A599" s="1" t="s">
         <v>19</v>
       </c>
@@ -26428,7 +26429,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="600" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A600" s="1" t="s">
         <v>19</v>
       </c>
@@ -26466,7 +26467,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="601" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A601" s="1" t="s">
         <v>19</v>
       </c>
@@ -26504,7 +26505,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="602" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A602" s="1" t="s">
         <v>19</v>
       </c>
@@ -26542,7 +26543,7 @@
         <v>27.7</v>
       </c>
     </row>
-    <row r="603" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A603" s="1" t="s">
         <v>19</v>
       </c>
@@ -26580,7 +26581,7 @@
         <v>27.4</v>
       </c>
     </row>
-    <row r="604" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A604" s="1" t="s">
         <v>19</v>
       </c>
@@ -26618,7 +26619,7 @@
         <v>27.2</v>
       </c>
     </row>
-    <row r="605" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A605" s="1" t="s">
         <v>19</v>
       </c>
@@ -26656,7 +26657,7 @@
         <v>27.4</v>
       </c>
     </row>
-    <row r="606" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A606" s="1" t="s">
         <v>19</v>
       </c>
@@ -26694,7 +26695,7 @@
         <v>27.9</v>
       </c>
     </row>
-    <row r="607" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A607" s="1" t="s">
         <v>19</v>
       </c>
@@ -26732,7 +26733,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="608" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A608" s="1" t="s">
         <v>19</v>
       </c>
@@ -26770,7 +26771,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="609" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A609" s="1" t="s">
         <v>19</v>
       </c>
@@ -26808,7 +26809,7 @@
         <v>25.7</v>
       </c>
     </row>
-    <row r="610" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A610" s="1" t="s">
         <v>19</v>
       </c>
@@ -26846,7 +26847,7 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="611" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A611" s="1" t="s">
         <v>19</v>
       </c>
@@ -26884,7 +26885,7 @@
         <v>27.8</v>
       </c>
     </row>
-    <row r="612" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A612" s="1" t="s">
         <v>19</v>
       </c>
@@ -26922,7 +26923,7 @@
         <v>27.4</v>
       </c>
     </row>
-    <row r="613" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A613" s="1" t="s">
         <v>19</v>
       </c>
@@ -26960,7 +26961,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="614" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A614" s="1" t="s">
         <v>19</v>
       </c>
@@ -26998,7 +26999,7 @@
         <v>27.1</v>
       </c>
     </row>
-    <row r="615" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A615" s="1" t="s">
         <v>19</v>
       </c>
@@ -27036,7 +27037,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="616" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A616" s="1" t="s">
         <v>19</v>
       </c>
@@ -27074,7 +27075,7 @@
         <v>27.8</v>
       </c>
     </row>
-    <row r="617" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A617" s="1" t="s">
         <v>19</v>
       </c>
@@ -27112,7 +27113,7 @@
         <v>27.8</v>
       </c>
     </row>
-    <row r="618" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A618" s="1" t="s">
         <v>19</v>
       </c>
@@ -27150,7 +27151,7 @@
         <v>27.4</v>
       </c>
     </row>
-    <row r="619" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A619" s="1" t="s">
         <v>19</v>
       </c>
@@ -27188,7 +27189,7 @@
         <v>27.8</v>
       </c>
     </row>
-    <row r="620" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A620" s="1" t="s">
         <v>19</v>
       </c>
@@ -27226,7 +27227,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="621" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A621" s="1" t="s">
         <v>19</v>
       </c>
@@ -27264,7 +27265,7 @@
         <v>27.3</v>
       </c>
     </row>
-    <row r="622" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A622" s="1" t="s">
         <v>19</v>
       </c>
@@ -27302,7 +27303,7 @@
         <v>27.8</v>
       </c>
     </row>
-    <row r="623" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A623" s="1" t="s">
         <v>19</v>
       </c>
@@ -27340,7 +27341,7 @@
         <v>27.4</v>
       </c>
     </row>
-    <row r="624" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A624" s="1" t="s">
         <v>19</v>
       </c>
@@ -27378,7 +27379,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="625" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A625" s="1" t="s">
         <v>19</v>
       </c>
@@ -27416,7 +27417,7 @@
         <v>27.8</v>
       </c>
     </row>
-    <row r="626" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A626" s="1" t="s">
         <v>19</v>
       </c>
@@ -27454,7 +27455,7 @@
         <v>27.7</v>
       </c>
     </row>
-    <row r="627" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A627" s="1" t="s">
         <v>19</v>
       </c>
@@ -27492,7 +27493,7 @@
         <v>27.2</v>
       </c>
     </row>
-    <row r="628" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A628" s="1" t="s">
         <v>19</v>
       </c>
@@ -27530,7 +27531,7 @@
         <v>27.2</v>
       </c>
     </row>
-    <row r="629" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A629" s="1" t="s">
         <v>19</v>
       </c>
@@ -27568,7 +27569,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="630" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A630" s="1" t="s">
         <v>19</v>
       </c>
@@ -27606,7 +27607,7 @@
         <v>27.4</v>
       </c>
     </row>
-    <row r="631" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A631" s="1" t="s">
         <v>19</v>
       </c>
@@ -27644,7 +27645,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="632" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A632" s="1" t="s">
         <v>19</v>
       </c>
@@ -27682,7 +27683,7 @@
         <v>27.4</v>
       </c>
     </row>
-    <row r="633" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A633" s="1" t="s">
         <v>19</v>
       </c>
@@ -27720,7 +27721,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="634" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A634" s="1" t="s">
         <v>19</v>
       </c>
@@ -27758,7 +27759,7 @@
         <v>27.8</v>
       </c>
     </row>
-    <row r="635" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A635" s="1" t="s">
         <v>19</v>
       </c>
@@ -27796,7 +27797,7 @@
         <v>27.9</v>
       </c>
     </row>
-    <row r="636" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A636" s="1" t="s">
         <v>19</v>
       </c>
@@ -27834,7 +27835,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="637" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A637" s="1" t="s">
         <v>19</v>
       </c>
@@ -27872,7 +27873,7 @@
         <v>28.2</v>
       </c>
     </row>
-    <row r="638" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A638" s="1" t="s">
         <v>19</v>
       </c>
@@ -27910,7 +27911,7 @@
         <v>27.4</v>
       </c>
     </row>
-    <row r="639" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A639" s="1" t="s">
         <v>19</v>
       </c>
@@ -27948,7 +27949,7 @@
         <v>27.2</v>
       </c>
     </row>
-    <row r="640" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A640" s="1" t="s">
         <v>19</v>
       </c>
@@ -27986,7 +27987,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="641" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A641" s="1" t="s">
         <v>19</v>
       </c>
@@ -28024,7 +28025,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="642" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A642" s="1" t="s">
         <v>19</v>
       </c>
@@ -28062,7 +28063,7 @@
         <v>28.2</v>
       </c>
     </row>
-    <row r="643" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A643" s="1" t="s">
         <v>19</v>
       </c>
@@ -28100,7 +28101,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="644" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A644" s="1" t="s">
         <v>19</v>
       </c>
@@ -28138,7 +28139,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="645" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A645" s="1" t="s">
         <v>19</v>
       </c>
@@ -28176,7 +28177,7 @@
         <v>27.4</v>
       </c>
     </row>
-    <row r="646" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A646" s="1" t="s">
         <v>19</v>
       </c>
@@ -28214,7 +28215,7 @@
         <v>27.4</v>
       </c>
     </row>
-    <row r="647" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A647" s="1" t="s">
         <v>19</v>
       </c>
@@ -28252,7 +28253,7 @@
         <v>27.9</v>
       </c>
     </row>
-    <row r="648" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A648" s="1" t="s">
         <v>19</v>
       </c>
@@ -28290,7 +28291,7 @@
         <v>32.6</v>
       </c>
     </row>
-    <row r="649" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A649" s="1" t="s">
         <v>19</v>
       </c>
@@ -28328,7 +28329,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="650" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A650" s="1" t="s">
         <v>19</v>
       </c>
@@ -28366,7 +28367,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="651" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A651" s="1" t="s">
         <v>19</v>
       </c>
@@ -28404,7 +28405,7 @@
         <v>27.7</v>
       </c>
     </row>
-    <row r="652" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A652" s="1" t="s">
         <v>19</v>
       </c>
@@ -28442,7 +28443,7 @@
         <v>28.2</v>
       </c>
     </row>
-    <row r="653" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A653" s="1" t="s">
         <v>19</v>
       </c>
@@ -28480,7 +28481,7 @@
         <v>27.2</v>
       </c>
     </row>
-    <row r="654" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A654" s="1" t="s">
         <v>19</v>
       </c>
@@ -28518,7 +28519,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="655" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A655" s="1" t="s">
         <v>19</v>
       </c>
@@ -28556,7 +28557,7 @@
         <v>26.9</v>
       </c>
     </row>
-    <row r="656" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A656" s="1" t="s">
         <v>19</v>
       </c>
@@ -28594,7 +28595,7 @@
         <v>25.9</v>
       </c>
     </row>
-    <row r="657" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A657" s="1" t="s">
         <v>19</v>
       </c>
@@ -28632,7 +28633,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="658" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A658" s="1" t="s">
         <v>19</v>
       </c>
@@ -28670,7 +28671,7 @@
         <v>27.9</v>
       </c>
     </row>
-    <row r="659" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A659" s="1" t="s">
         <v>19</v>
       </c>
@@ -28708,7 +28709,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="660" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A660" s="1" t="s">
         <v>19</v>
       </c>
@@ -28746,7 +28747,7 @@
         <v>27.7</v>
       </c>
     </row>
-    <row r="661" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A661" s="1" t="s">
         <v>19</v>
       </c>
@@ -28784,7 +28785,7 @@
         <v>27.7</v>
       </c>
     </row>
-    <row r="662" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A662" s="1" t="s">
         <v>19</v>
       </c>
@@ -28822,7 +28823,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="663" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A663" s="1" t="s">
         <v>19</v>
       </c>
@@ -28860,7 +28861,7 @@
         <v>27.7</v>
       </c>
     </row>
-    <row r="664" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A664" s="1" t="s">
         <v>19</v>
       </c>
@@ -28898,7 +28899,7 @@
         <v>27.2</v>
       </c>
     </row>
-    <row r="665" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A665" s="1" t="s">
         <v>19</v>
       </c>
@@ -28936,7 +28937,7 @@
         <v>27.4</v>
       </c>
     </row>
-    <row r="666" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A666" s="1" t="s">
         <v>19</v>
       </c>
@@ -28974,7 +28975,7 @@
         <v>27.7</v>
       </c>
     </row>
-    <row r="667" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A667" s="1" t="s">
         <v>19</v>
       </c>
@@ -29012,7 +29013,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="668" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A668" s="1" t="s">
         <v>19</v>
       </c>
@@ -29050,7 +29051,7 @@
         <v>27.7</v>
       </c>
     </row>
-    <row r="669" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A669" s="1" t="s">
         <v>19</v>
       </c>
@@ -29088,7 +29089,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="670" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A670" s="1" t="s">
         <v>19</v>
       </c>
@@ -29126,7 +29127,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="671" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A671" s="1" t="s">
         <v>19</v>
       </c>
@@ -29164,7 +29165,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="672" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A672" s="1" t="s">
         <v>19</v>
       </c>
@@ -29202,7 +29203,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="673" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A673" s="1" t="s">
         <v>19</v>
       </c>
@@ -29240,7 +29241,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="674" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A674" s="1" t="s">
         <v>19</v>
       </c>
@@ -29278,7 +29279,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="675" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A675" s="1" t="s">
         <v>19</v>
       </c>
@@ -29316,7 +29317,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="676" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A676" s="1" t="s">
         <v>19</v>
       </c>
@@ -29354,7 +29355,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="677" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A677" s="1" t="s">
         <v>19</v>
       </c>
@@ -29392,7 +29393,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="678" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A678" s="1" t="s">
         <v>19</v>
       </c>
@@ -29430,7 +29431,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="679" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A679" s="1" t="s">
         <v>19</v>
       </c>
@@ -29468,7 +29469,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="680" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A680" s="1" t="s">
         <v>19</v>
       </c>
@@ -29506,7 +29507,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="681" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A681" s="1" t="s">
         <v>19</v>
       </c>
@@ -29544,7 +29545,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="682" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A682" s="1" t="s">
         <v>19</v>
       </c>
@@ -29582,7 +29583,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="683" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A683" s="1" t="s">
         <v>19</v>
       </c>
@@ -29620,7 +29621,7 @@
         <v>27.1</v>
       </c>
     </row>
-    <row r="684" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A684" s="1" t="s">
         <v>19</v>
       </c>
@@ -29658,7 +29659,7 @@
         <v>27.7</v>
       </c>
     </row>
-    <row r="685" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A685" s="1" t="s">
         <v>19</v>
       </c>
@@ -29696,7 +29697,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="686" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A686" s="1" t="s">
         <v>19</v>
       </c>
@@ -29734,7 +29735,7 @@
         <v>27.9</v>
       </c>
     </row>
-    <row r="687" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A687" s="1" t="s">
         <v>19</v>
       </c>
@@ -29772,7 +29773,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="688" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A688" s="1" t="s">
         <v>19</v>
       </c>
@@ -29810,7 +29811,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="689" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A689" s="1" t="s">
         <v>19</v>
       </c>
@@ -29848,7 +29849,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="690" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A690" s="1" t="s">
         <v>19</v>
       </c>
@@ -29886,7 +29887,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="691" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A691" s="1" t="s">
         <v>19</v>
       </c>
@@ -29924,7 +29925,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="692" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A692" s="1" t="s">
         <v>19</v>
       </c>
@@ -29962,7 +29963,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="693" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A693" s="1" t="s">
         <v>19</v>
       </c>
@@ -30000,7 +30001,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="694" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F694" s="1" t="s">
         <v>93</v>
       </c>
@@ -30020,7 +30021,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="695" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F695" s="1" t="s">
         <v>976</v>
       </c>
@@ -30040,7 +30041,7 @@
         <v>6674.1</v>
       </c>
     </row>
-    <row r="696" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A696" s="1" t="s">
         <v>19</v>
       </c>
@@ -30078,7 +30079,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="697" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A697" s="1" t="s">
         <v>19</v>
       </c>
@@ -30116,7 +30117,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="698" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A698" s="1" t="s">
         <v>19</v>
       </c>
@@ -30154,7 +30155,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="699" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A699" s="1" t="s">
         <v>19</v>
       </c>
@@ -30192,7 +30193,7 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="700" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A700" s="1" t="s">
         <v>19</v>
       </c>
@@ -30230,7 +30231,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="701" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A701" s="1" t="s">
         <v>19</v>
       </c>
@@ -30268,7 +30269,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="702" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A702" s="1" t="s">
         <v>19</v>
       </c>
@@ -30306,7 +30307,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="703" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A703" s="1" t="s">
         <v>19</v>
       </c>
@@ -30344,7 +30345,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="704" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A704" s="1" t="s">
         <v>19</v>
       </c>
@@ -30382,7 +30383,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="705" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A705" s="1" t="s">
         <v>19</v>
       </c>
@@ -30420,7 +30421,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="706" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A706" s="1" t="s">
         <v>19</v>
       </c>
@@ -30458,7 +30459,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="707" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A707" s="1" t="s">
         <v>19</v>
       </c>
@@ -30496,7 +30497,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="708" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A708" s="1" t="s">
         <v>19</v>
       </c>
@@ -30534,7 +30535,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="709" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A709" s="1" t="s">
         <v>19</v>
       </c>
@@ -30572,7 +30573,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="710" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A710" s="1" t="s">
         <v>19</v>
       </c>
@@ -30610,7 +30611,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="711" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A711" s="1" t="s">
         <v>19</v>
       </c>
@@ -30648,7 +30649,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="712" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A712" s="1" t="s">
         <v>19</v>
       </c>
@@ -30686,7 +30687,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="713" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A713" s="1" t="s">
         <v>19</v>
       </c>
@@ -30724,7 +30725,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="714" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A714" s="1" t="s">
         <v>19</v>
       </c>
@@ -30762,7 +30763,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="715" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A715" s="1" t="s">
         <v>19</v>
       </c>
@@ -30800,7 +30801,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="716" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A716" s="1" t="s">
         <v>19</v>
       </c>
@@ -30838,7 +30839,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="717" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A717" s="1" t="s">
         <v>19</v>
       </c>
@@ -30876,7 +30877,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="718" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A718" s="1" t="s">
         <v>19</v>
       </c>
@@ -30914,7 +30915,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="719" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A719" s="1" t="s">
         <v>19</v>
       </c>
@@ -30952,7 +30953,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="720" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A720" s="1" t="s">
         <v>19</v>
       </c>
@@ -30990,7 +30991,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="721" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A721" s="1" t="s">
         <v>19</v>
       </c>
@@ -31028,7 +31029,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="722" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A722" s="1" t="s">
         <v>19</v>
       </c>
@@ -31066,7 +31067,7 @@
         <v>30.7</v>
       </c>
     </row>
-    <row r="723" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A723" s="1" t="s">
         <v>19</v>
       </c>
@@ -31104,7 +31105,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="724" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A724" s="1" t="s">
         <v>19</v>
       </c>
@@ -31142,7 +31143,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="725" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A725" s="1" t="s">
         <v>19</v>
       </c>
@@ -31180,7 +31181,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="726" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A726" s="1" t="s">
         <v>19</v>
       </c>
@@ -31218,7 +31219,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="727" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A727" s="1" t="s">
         <v>19</v>
       </c>
@@ -31256,7 +31257,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="728" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A728" s="1" t="s">
         <v>19</v>
       </c>
@@ -31294,7 +31295,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="729" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A729" s="1" t="s">
         <v>19</v>
       </c>
@@ -31332,7 +31333,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="730" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A730" s="1" t="s">
         <v>19</v>
       </c>
@@ -31370,7 +31371,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="731" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F731" s="1" t="s">
         <v>93</v>
       </c>
@@ -31390,7 +31391,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="732" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F732" s="1" t="s">
         <v>1015</v>
       </c>
@@ -31410,7 +31411,7 @@
         <v>831.3</v>
       </c>
     </row>
-    <row r="733" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A733" s="1" t="s">
         <v>19</v>
       </c>
@@ -31448,7 +31449,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="734" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A734" s="1" t="s">
         <v>19</v>
       </c>
@@ -31486,7 +31487,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="735" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A735" s="1" t="s">
         <v>19</v>
       </c>
@@ -31524,7 +31525,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="736" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A736" s="1" t="s">
         <v>19</v>
       </c>
@@ -31562,7 +31563,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="737" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A737" s="1" t="s">
         <v>19</v>
       </c>
@@ -31600,7 +31601,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="738" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A738" s="1" t="s">
         <v>19</v>
       </c>
@@ -31638,7 +31639,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="739" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A739" s="1" t="s">
         <v>19</v>
       </c>
@@ -31676,7 +31677,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="740" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A740" s="1" t="s">
         <v>19</v>
       </c>
@@ -31714,7 +31715,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="741" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A741" s="1" t="s">
         <v>19</v>
       </c>
@@ -31752,7 +31753,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="742" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A742" s="1" t="s">
         <v>19</v>
       </c>
@@ -31790,7 +31791,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="743" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A743" s="1" t="s">
         <v>19</v>
       </c>
@@ -31828,7 +31829,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="744" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A744" s="1" t="s">
         <v>19</v>
       </c>
@@ -31866,7 +31867,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="745" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A745" s="1" t="s">
         <v>19</v>
       </c>
@@ -31904,7 +31905,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="746" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A746" s="1" t="s">
         <v>19</v>
       </c>
@@ -31942,7 +31943,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="747" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A747" s="1" t="s">
         <v>19</v>
       </c>
@@ -31980,7 +31981,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="748" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A748" s="1" t="s">
         <v>19</v>
       </c>
@@ -32018,7 +32019,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="749" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A749" s="1" t="s">
         <v>19</v>
       </c>
@@ -32056,7 +32057,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="750" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A750" s="1" t="s">
         <v>19</v>
       </c>
@@ -32094,7 +32095,7 @@
         <v>33.6</v>
       </c>
     </row>
-    <row r="751" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A751" s="1" t="s">
         <v>19</v>
       </c>
@@ -32132,7 +32133,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="752" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A752" s="1" t="s">
         <v>19</v>
       </c>
@@ -32170,7 +32171,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="753" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A753" s="1" t="s">
         <v>19</v>
       </c>
@@ -32208,7 +32209,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="754" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A754" s="1" t="s">
         <v>19</v>
       </c>
@@ -32246,7 +32247,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="755" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F755" s="1" t="s">
         <v>93</v>
       </c>
@@ -32266,7 +32267,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="756" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F756" s="1" t="s">
         <v>121</v>
       </c>
@@ -32286,7 +32287,7 @@
         <v>545.70000000000005</v>
       </c>
     </row>
-    <row r="757" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A757" s="1" t="s">
         <v>19</v>
       </c>
@@ -32324,7 +32325,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="758" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A758" s="1" t="s">
         <v>19</v>
       </c>
@@ -32362,7 +32363,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="759" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A759" s="1" t="s">
         <v>19</v>
       </c>
@@ -32400,7 +32401,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="760" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A760" s="1" t="s">
         <v>19</v>
       </c>
@@ -32438,7 +32439,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="761" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A761" s="1" t="s">
         <v>19</v>
       </c>
@@ -32476,7 +32477,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="762" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A762" s="1" t="s">
         <v>19</v>
       </c>
@@ -32514,7 +32515,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="763" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A763" s="1" t="s">
         <v>19</v>
       </c>
@@ -32552,7 +32553,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="764" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A764" s="1" t="s">
         <v>19</v>
       </c>
@@ -32590,7 +32591,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="765" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A765" s="1" t="s">
         <v>19</v>
       </c>
@@ -32628,7 +32629,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="766" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A766" s="1" t="s">
         <v>19</v>
       </c>
@@ -32666,7 +32667,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="767" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A767" s="1" t="s">
         <v>19</v>
       </c>
@@ -32704,7 +32705,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="768" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A768" s="1" t="s">
         <v>19</v>
       </c>
@@ -32742,7 +32743,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="769" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A769" s="1" t="s">
         <v>19</v>
       </c>
@@ -32780,7 +32781,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="770" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A770" s="1" t="s">
         <v>19</v>
       </c>
@@ -32818,7 +32819,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="771" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A771" s="1" t="s">
         <v>19</v>
       </c>
@@ -32856,7 +32857,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="772" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A772" s="1" t="s">
         <v>19</v>
       </c>
@@ -32894,7 +32895,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="773" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A773" s="1" t="s">
         <v>19</v>
       </c>
@@ -32932,7 +32933,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="774" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A774" s="1" t="s">
         <v>19</v>
       </c>
@@ -32970,7 +32971,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="775" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A775" s="1" t="s">
         <v>19</v>
       </c>
@@ -33008,7 +33009,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="776" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A776" s="1" t="s">
         <v>19</v>
       </c>
@@ -33046,7 +33047,7 @@
         <v>25.35</v>
       </c>
     </row>
-    <row r="777" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A777" s="1" t="s">
         <v>19</v>
       </c>
@@ -33084,7 +33085,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="778" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A778" s="1" t="s">
         <v>19</v>
       </c>
@@ -33122,7 +33123,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="779" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A779" s="1" t="s">
         <v>19</v>
       </c>
@@ -33160,7 +33161,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="780" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A780" s="1" t="s">
         <v>19</v>
       </c>
@@ -33198,7 +33199,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="781" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A781" s="1" t="s">
         <v>19</v>
       </c>
@@ -33236,7 +33237,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="782" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A782" s="1" t="s">
         <v>19</v>
       </c>
@@ -33274,7 +33275,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="783" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A783" s="1" t="s">
         <v>19</v>
       </c>
@@ -33312,7 +33313,7 @@
         <v>25.2</v>
       </c>
     </row>
-    <row r="784" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A784" s="1" t="s">
         <v>19</v>
       </c>
@@ -33350,7 +33351,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="785" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A785" s="1" t="s">
         <v>19</v>
       </c>
@@ -33388,7 +33389,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="786" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A786" s="1" t="s">
         <v>19</v>
       </c>
@@ -33426,7 +33427,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="787" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A787" s="1" t="s">
         <v>19</v>
       </c>
@@ -33464,7 +33465,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="788" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A788" s="1" t="s">
         <v>19</v>
       </c>
@@ -33502,7 +33503,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="789" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A789" s="1" t="s">
         <v>19</v>
       </c>
@@ -33540,7 +33541,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="790" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A790" s="1" t="s">
         <v>19</v>
       </c>
@@ -33578,7 +33579,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="791" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F791" s="1" t="s">
         <v>93</v>
       </c>
@@ -33598,7 +33599,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="792" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F792" s="1" t="s">
         <v>95</v>
       </c>
@@ -33618,7 +33619,7 @@
         <v>839.55</v>
       </c>
     </row>
-    <row r="793" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A793" s="1" t="s">
         <v>19</v>
       </c>
@@ -33656,7 +33657,7 @@
         <v>26.2</v>
       </c>
     </row>
-    <row r="794" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A794" s="1" t="s">
         <v>19</v>
       </c>
@@ -33694,7 +33695,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="795" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A795" s="1" t="s">
         <v>19</v>
       </c>
@@ -33732,7 +33733,7 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="796" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A796" s="1" t="s">
         <v>19</v>
       </c>
@@ -33770,7 +33771,7 @@
         <v>26.2</v>
       </c>
     </row>
-    <row r="797" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A797" s="1" t="s">
         <v>19</v>
       </c>
@@ -33808,7 +33809,7 @@
         <v>26.4</v>
       </c>
     </row>
-    <row r="798" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A798" s="1" t="s">
         <v>19</v>
       </c>
@@ -33846,7 +33847,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="799" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A799" s="1" t="s">
         <v>19</v>
       </c>
@@ -33884,7 +33885,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="800" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A800" s="1" t="s">
         <v>19</v>
       </c>
@@ -33922,7 +33923,7 @@
         <v>26.2</v>
       </c>
     </row>
-    <row r="801" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A801" s="1" t="s">
         <v>19</v>
       </c>
@@ -33960,7 +33961,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="802" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A802" s="1" t="s">
         <v>19</v>
       </c>
@@ -33998,7 +33999,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="803" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A803" s="1" t="s">
         <v>19</v>
       </c>
@@ -34036,7 +34037,7 @@
         <v>26.2</v>
       </c>
     </row>
-    <row r="804" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A804" s="1" t="s">
         <v>19</v>
       </c>
@@ -34074,7 +34075,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="805" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A805" s="1" t="s">
         <v>19</v>
       </c>
@@ -34112,7 +34113,7 @@
         <v>26.2</v>
       </c>
     </row>
-    <row r="806" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A806" s="1" t="s">
         <v>19</v>
       </c>
@@ -34150,7 +34151,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="807" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A807" s="1" t="s">
         <v>19</v>
       </c>
@@ -34188,7 +34189,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="808" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A808" s="1" t="s">
         <v>19</v>
       </c>
@@ -34226,7 +34227,7 @@
         <v>25.4</v>
       </c>
     </row>
-    <row r="809" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A809" s="1" t="s">
         <v>19</v>
       </c>
@@ -34264,7 +34265,7 @@
         <v>26.4</v>
       </c>
     </row>
-    <row r="810" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A810" s="1" t="s">
         <v>19</v>
       </c>
@@ -34302,7 +34303,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="811" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A811" s="1" t="s">
         <v>19</v>
       </c>
@@ -34340,7 +34341,7 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="812" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A812" s="1" t="s">
         <v>19</v>
       </c>
@@ -34378,7 +34379,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="813" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A813" s="1" t="s">
         <v>19</v>
       </c>
@@ -34416,7 +34417,7 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="814" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A814" s="1" t="s">
         <v>19</v>
       </c>
@@ -34454,7 +34455,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="815" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A815" s="1" t="s">
         <v>19</v>
       </c>
@@ -34492,7 +34493,7 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="816" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A816" s="1" t="s">
         <v>19</v>
       </c>
@@ -34530,7 +34531,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="817" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A817" s="1" t="s">
         <v>19</v>
       </c>
@@ -34568,7 +34569,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="818" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A818" s="1" t="s">
         <v>19</v>
       </c>
@@ -34606,7 +34607,7 @@
         <v>27.1</v>
       </c>
     </row>
-    <row r="819" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A819" s="1" t="s">
         <v>19</v>
       </c>
@@ -34644,7 +34645,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="820" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A820" s="1" t="s">
         <v>19</v>
       </c>
@@ -34682,7 +34683,7 @@
         <v>27.3</v>
       </c>
     </row>
-    <row r="821" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A821" s="1" t="s">
         <v>19</v>
       </c>
@@ -34720,7 +34721,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="822" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A822" s="1" t="s">
         <v>19</v>
       </c>
@@ -34758,7 +34759,7 @@
         <v>27.3</v>
       </c>
     </row>
-    <row r="823" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A823" s="1" t="s">
         <v>19</v>
       </c>
@@ -34796,7 +34797,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="824" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A824" s="1" t="s">
         <v>19</v>
       </c>
@@ -34834,7 +34835,7 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="825" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A825" s="1" t="s">
         <v>19</v>
       </c>
@@ -34872,7 +34873,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="826" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A826" s="1" t="s">
         <v>19</v>
       </c>
@@ -34910,7 +34911,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="827" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A827" s="1" t="s">
         <v>19</v>
       </c>
@@ -34948,7 +34949,7 @@
         <v>27.2</v>
       </c>
     </row>
-    <row r="828" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A828" s="1" t="s">
         <v>19</v>
       </c>
@@ -34986,7 +34987,7 @@
         <v>27.1</v>
       </c>
     </row>
-    <row r="829" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A829" s="1" t="s">
         <v>19</v>
       </c>
@@ -35024,7 +35025,7 @@
         <v>27.2</v>
       </c>
     </row>
-    <row r="830" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A830" s="1" t="s">
         <v>19</v>
       </c>
@@ -35062,7 +35063,7 @@
         <v>27.1</v>
       </c>
     </row>
-    <row r="831" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A831" s="1" t="s">
         <v>19</v>
       </c>
@@ -35100,7 +35101,7 @@
         <v>27.1</v>
       </c>
     </row>
-    <row r="832" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A832" s="1" t="s">
         <v>19</v>
       </c>
@@ -35138,7 +35139,7 @@
         <v>26.9</v>
       </c>
     </row>
-    <row r="833" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A833" s="1" t="s">
         <v>19</v>
       </c>
@@ -35176,7 +35177,7 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="834" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A834" s="1" t="s">
         <v>19</v>
       </c>
@@ -35214,7 +35215,7 @@
         <v>27.2</v>
       </c>
     </row>
-    <row r="835" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A835" s="1" t="s">
         <v>19</v>
       </c>
@@ -35252,7 +35253,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="836" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A836" s="1" t="s">
         <v>19</v>
       </c>
@@ -35290,7 +35291,7 @@
         <v>27.2</v>
       </c>
     </row>
-    <row r="837" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A837" s="1" t="s">
         <v>19</v>
       </c>
@@ -35328,7 +35329,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="838" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A838" s="1" t="s">
         <v>19</v>
       </c>
@@ -35366,7 +35367,7 @@
         <v>26.2</v>
       </c>
     </row>
-    <row r="839" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A839" s="1" t="s">
         <v>19</v>
       </c>
@@ -35404,7 +35405,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="840" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A840" s="1" t="s">
         <v>19</v>
       </c>
@@ -35442,7 +35443,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="841" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A841" s="1" t="s">
         <v>19</v>
       </c>
@@ -35480,7 +35481,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="842" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A842" s="1" t="s">
         <v>19</v>
       </c>
@@ -35518,7 +35519,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="843" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A843" s="1" t="s">
         <v>19</v>
       </c>
@@ -35556,7 +35557,7 @@
         <v>26.9</v>
       </c>
     </row>
-    <row r="844" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A844" s="1" t="s">
         <v>19</v>
       </c>
@@ -35594,7 +35595,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="845" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A845" s="1" t="s">
         <v>19</v>
       </c>
@@ -35632,7 +35633,7 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="846" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A846" s="1" t="s">
         <v>19</v>
       </c>
@@ -35670,7 +35671,7 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="847" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A847" s="1" t="s">
         <v>19</v>
       </c>
@@ -35708,7 +35709,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="848" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A848" s="1" t="s">
         <v>19</v>
       </c>
@@ -35746,7 +35747,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="849" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A849" s="1" t="s">
         <v>19</v>
       </c>
@@ -35784,7 +35785,7 @@
         <v>25.7</v>
       </c>
     </row>
-    <row r="850" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A850" s="1" t="s">
         <v>19</v>
       </c>
@@ -35822,7 +35823,7 @@
         <v>25.9</v>
       </c>
     </row>
-    <row r="851" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A851" s="1" t="s">
         <v>19</v>
       </c>
@@ -35860,7 +35861,7 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="852" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A852" s="1" t="s">
         <v>19</v>
       </c>
@@ -35898,7 +35899,7 @@
         <v>26.4</v>
       </c>
     </row>
-    <row r="853" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F853" s="1" t="s">
         <v>93</v>
       </c>
@@ -35918,7 +35919,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="854" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F854" s="1" t="s">
         <v>592</v>
       </c>
@@ -35938,7 +35939,7 @@
         <v>1578.9</v>
       </c>
     </row>
-    <row r="855" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A855" s="1" t="s">
         <v>19</v>
       </c>
@@ -35976,7 +35977,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="856" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A856" s="1" t="s">
         <v>19</v>
       </c>
@@ -36014,7 +36015,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="857" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A857" s="1" t="s">
         <v>19</v>
       </c>
@@ -36052,7 +36053,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="858" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A858" s="1" t="s">
         <v>19</v>
       </c>
@@ -36090,7 +36091,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="859" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A859" s="1" t="s">
         <v>19</v>
       </c>
@@ -36128,7 +36129,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="860" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A860" s="1" t="s">
         <v>19</v>
       </c>
@@ -36166,7 +36167,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="861" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A861" s="1" t="s">
         <v>19</v>
       </c>
@@ -36204,7 +36205,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="862" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A862" s="1" t="s">
         <v>19</v>
       </c>
@@ -36242,7 +36243,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="863" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A863" s="1" t="s">
         <v>19</v>
       </c>
@@ -36280,7 +36281,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="864" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A864" s="1" t="s">
         <v>19</v>
       </c>
@@ -36318,7 +36319,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="865" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A865" s="1" t="s">
         <v>19</v>
       </c>
@@ -36356,7 +36357,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="866" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A866" s="1" t="s">
         <v>19</v>
       </c>
@@ -36394,7 +36395,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="867" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A867" s="1" t="s">
         <v>19</v>
       </c>
@@ -36432,7 +36433,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="868" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A868" s="1" t="s">
         <v>19</v>
       </c>
@@ -36470,7 +36471,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="869" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A869" s="1" t="s">
         <v>19</v>
       </c>
@@ -36508,7 +36509,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="870" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A870" s="1" t="s">
         <v>19</v>
       </c>
@@ -36546,7 +36547,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="871" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A871" s="1" t="s">
         <v>19</v>
       </c>
@@ -36584,7 +36585,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="872" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A872" s="1" t="s">
         <v>19</v>
       </c>
@@ -36622,7 +36623,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="873" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A873" s="1" t="s">
         <v>19</v>
       </c>
@@ -36660,7 +36661,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="874" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A874" s="1" t="s">
         <v>19</v>
       </c>
@@ -36698,7 +36699,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="875" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A875" s="1" t="s">
         <v>19</v>
       </c>
@@ -36736,7 +36737,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="876" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A876" s="1" t="s">
         <v>19</v>
       </c>
@@ -36774,7 +36775,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="877" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A877" s="1" t="s">
         <v>19</v>
       </c>
@@ -36812,7 +36813,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="878" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A878" s="1" t="s">
         <v>19</v>
       </c>
@@ -36850,7 +36851,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="879" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A879" s="1" t="s">
         <v>19</v>
       </c>
@@ -36888,7 +36889,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="880" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A880" s="1" t="s">
         <v>19</v>
       </c>
@@ -36926,7 +36927,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="881" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A881" s="1" t="s">
         <v>19</v>
       </c>
@@ -36964,7 +36965,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="882" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A882" s="1" t="s">
         <v>19</v>
       </c>
@@ -37002,7 +37003,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="883" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A883" s="1" t="s">
         <v>19</v>
       </c>
@@ -37040,7 +37041,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="884" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A884" s="1" t="s">
         <v>19</v>
       </c>
@@ -37078,7 +37079,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="885" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A885" s="1" t="s">
         <v>19</v>
       </c>
@@ -37116,7 +37117,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="886" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A886" s="1" t="s">
         <v>19</v>
       </c>
@@ -37154,7 +37155,7 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="887" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A887" s="1" t="s">
         <v>19</v>
       </c>
@@ -37192,7 +37193,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="888" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A888" s="1" t="s">
         <v>19</v>
       </c>
@@ -37230,7 +37231,7 @@
         <v>30.3</v>
       </c>
     </row>
-    <row r="889" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F889" s="1" t="s">
         <v>93</v>
       </c>
@@ -37250,7 +37251,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="890" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F890" s="1" t="s">
         <v>95</v>
       </c>
@@ -37270,7 +37271,7 @@
         <v>806.7</v>
       </c>
     </row>
-    <row r="891" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A891" s="1" t="s">
         <v>19</v>
       </c>
@@ -37308,7 +37309,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="892" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A892" s="1" t="s">
         <v>19</v>
       </c>
@@ -37346,7 +37347,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="893" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A893" s="1" t="s">
         <v>19</v>
       </c>
@@ -37384,7 +37385,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="894" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A894" s="1" t="s">
         <v>19</v>
       </c>
@@ -37422,7 +37423,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="895" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A895" s="1" t="s">
         <v>19</v>
       </c>
@@ -37460,7 +37461,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="896" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A896" s="1" t="s">
         <v>19</v>
       </c>
@@ -37498,7 +37499,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="897" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A897" s="1" t="s">
         <v>19</v>
       </c>
@@ -37536,7 +37537,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="898" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A898" s="1" t="s">
         <v>19</v>
       </c>
@@ -37574,7 +37575,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="899" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A899" s="1" t="s">
         <v>19</v>
       </c>
@@ -37612,7 +37613,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="900" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A900" s="1" t="s">
         <v>19</v>
       </c>
@@ -37650,7 +37651,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="901" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A901" s="1" t="s">
         <v>19</v>
       </c>
@@ -37688,7 +37689,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="902" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A902" s="1" t="s">
         <v>19</v>
       </c>
@@ -37726,7 +37727,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="903" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A903" s="1" t="s">
         <v>19</v>
       </c>
@@ -37764,7 +37765,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="904" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A904" s="1" t="s">
         <v>19</v>
       </c>
@@ -37802,7 +37803,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="905" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A905" s="1" t="s">
         <v>19</v>
       </c>
@@ -37840,7 +37841,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="906" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A906" s="1" t="s">
         <v>19</v>
       </c>
@@ -37878,7 +37879,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="907" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A907" s="1" t="s">
         <v>19</v>
       </c>
@@ -37916,7 +37917,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="908" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A908" s="1" t="s">
         <v>19</v>
       </c>
@@ -37954,7 +37955,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="909" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A909" s="1" t="s">
         <v>19</v>
       </c>
@@ -37992,7 +37993,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="910" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A910" s="1" t="s">
         <v>19</v>
       </c>
@@ -38030,7 +38031,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="911" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A911" s="1" t="s">
         <v>19</v>
       </c>
@@ -38068,7 +38069,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="912" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A912" s="1" t="s">
         <v>19</v>
       </c>
@@ -38106,7 +38107,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="913" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A913" s="1" t="s">
         <v>19</v>
       </c>
@@ -38144,7 +38145,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="914" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A914" s="1" t="s">
         <v>19</v>
       </c>
@@ -38182,7 +38183,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="915" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A915" s="1" t="s">
         <v>19</v>
       </c>
@@ -38220,7 +38221,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="916" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A916" s="1" t="s">
         <v>19</v>
       </c>
@@ -38258,7 +38259,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="917" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A917" s="1" t="s">
         <v>19</v>
       </c>
@@ -38296,7 +38297,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="918" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A918" s="1" t="s">
         <v>19</v>
       </c>
@@ -38334,7 +38335,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="919" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A919" s="1" t="s">
         <v>19</v>
       </c>
@@ -38372,7 +38373,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="920" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A920" s="1" t="s">
         <v>19</v>
       </c>
@@ -38410,7 +38411,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="921" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A921" s="1" t="s">
         <v>19</v>
       </c>
@@ -38448,7 +38449,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="922" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A922" s="1" t="s">
         <v>19</v>
       </c>
@@ -38486,7 +38487,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="923" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A923" s="1" t="s">
         <v>19</v>
       </c>
@@ -38524,7 +38525,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="924" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A924" s="1" t="s">
         <v>19</v>
       </c>
@@ -38562,7 +38563,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="925" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F925" s="1" t="s">
         <v>93</v>
       </c>
@@ -38582,7 +38583,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="926" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F926" s="1" t="s">
         <v>95</v>
       </c>
@@ -38602,7 +38603,7 @@
         <v>786.6</v>
       </c>
     </row>
-    <row r="927" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F927" s="1" t="s">
         <v>93</v>
       </c>
@@ -38622,7 +38623,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="928" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F928" s="1" t="s">
         <v>1213</v>
       </c>
@@ -38642,7 +38643,7 @@
         <v>22688.45</v>
       </c>
     </row>
-    <row r="929" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A929" s="1" t="s">
         <v>1214</v>
       </c>
@@ -38680,7 +38681,7 @@
         <v>55.4</v>
       </c>
     </row>
-    <row r="930" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F930" s="1" t="s">
         <v>93</v>
       </c>
@@ -38700,7 +38701,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="931" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F931" s="1" t="s">
         <v>1218</v>
       </c>
@@ -38720,7 +38721,7 @@
         <v>55.4</v>
       </c>
     </row>
-    <row r="932" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A932" s="1" t="s">
         <v>1214</v>
       </c>
@@ -38758,7 +38759,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="933" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F933" s="1" t="s">
         <v>93</v>
       </c>
@@ -38778,7 +38779,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="934" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F934" s="1" t="s">
         <v>1218</v>
       </c>
@@ -38798,7 +38799,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="935" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A935" s="1" t="s">
         <v>1214</v>
       </c>
@@ -38836,7 +38837,7 @@
         <v>165.8</v>
       </c>
     </row>
-    <row r="936" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F936" s="1" t="s">
         <v>93</v>
       </c>
@@ -38856,7 +38857,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="937" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F937" s="1" t="s">
         <v>1218</v>
       </c>
@@ -38876,7 +38877,7 @@
         <v>165.8</v>
       </c>
     </row>
-    <row r="938" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A938" s="1" t="s">
         <v>1214</v>
       </c>
@@ -38914,7 +38915,7 @@
         <v>55.8</v>
       </c>
     </row>
-    <row r="939" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F939" s="1" t="s">
         <v>93</v>
       </c>
@@ -38934,7 +38935,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="940" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F940" s="1" t="s">
         <v>1218</v>
       </c>
@@ -38954,7 +38955,7 @@
         <v>55.8</v>
       </c>
     </row>
-    <row r="941" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A941" s="1" t="s">
         <v>1214</v>
       </c>
@@ -38992,7 +38993,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="942" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F942" s="1" t="s">
         <v>93</v>
       </c>
@@ -39012,7 +39013,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="943" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F943" s="1" t="s">
         <v>1218</v>
       </c>
@@ -39032,7 +39033,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="944" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A944" s="1" t="s">
         <v>1214</v>
       </c>
@@ -39070,7 +39071,7 @@
         <v>168.4</v>
       </c>
     </row>
-    <row r="945" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F945" s="1" t="s">
         <v>93</v>
       </c>
@@ -39090,7 +39091,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="946" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F946" s="1" t="s">
         <v>1218</v>
       </c>
@@ -39110,7 +39111,7 @@
         <v>168.4</v>
       </c>
     </row>
-    <row r="947" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A947" s="1" t="s">
         <v>1214</v>
       </c>
@@ -39148,7 +39149,7 @@
         <v>96.3</v>
       </c>
     </row>
-    <row r="948" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F948" s="1" t="s">
         <v>93</v>
       </c>
@@ -39168,7 +39169,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="949" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="949" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F949" s="1" t="s">
         <v>1218</v>
       </c>
@@ -39188,7 +39189,7 @@
         <v>96.3</v>
       </c>
     </row>
-    <row r="950" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="950" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A950" s="1" t="s">
         <v>1214</v>
       </c>
@@ -39226,7 +39227,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="951" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F951" s="1" t="s">
         <v>93</v>
       </c>
@@ -39246,7 +39247,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="952" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F952" s="1" t="s">
         <v>1218</v>
       </c>
@@ -39266,7 +39267,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="953" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="953" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A953" s="1" t="s">
         <v>1214</v>
       </c>
@@ -39304,7 +39305,7 @@
         <v>56.4</v>
       </c>
     </row>
-    <row r="954" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="954" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F954" s="1" t="s">
         <v>93</v>
       </c>
@@ -39324,7 +39325,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="955" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F955" s="1" t="s">
         <v>1218</v>
       </c>
@@ -39344,7 +39345,7 @@
         <v>56.4</v>
       </c>
     </row>
-    <row r="956" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="956" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A956" s="1" t="s">
         <v>1214</v>
       </c>
@@ -39382,7 +39383,7 @@
         <v>37.4</v>
       </c>
     </row>
-    <row r="957" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F957" s="1" t="s">
         <v>93</v>
       </c>
@@ -39402,7 +39403,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="958" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="958" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F958" s="1" t="s">
         <v>1218</v>
       </c>
@@ -39422,7 +39423,7 @@
         <v>37.4</v>
       </c>
     </row>
-    <row r="959" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="959" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A959" s="1" t="s">
         <v>1214</v>
       </c>
@@ -39460,7 +39461,7 @@
         <v>46.9</v>
       </c>
     </row>
-    <row r="960" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="960" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F960" s="1" t="s">
         <v>93</v>
       </c>
@@ -39480,7 +39481,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="961" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F961" s="1" t="s">
         <v>1218</v>
       </c>
@@ -39500,7 +39501,7 @@
         <v>46.9</v>
       </c>
     </row>
-    <row r="962" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A962" s="1" t="s">
         <v>1214</v>
       </c>
@@ -39538,7 +39539,7 @@
         <v>91.3</v>
       </c>
     </row>
-    <row r="963" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="963" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F963" s="1" t="s">
         <v>93</v>
       </c>
@@ -39558,7 +39559,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="964" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="964" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F964" s="1" t="s">
         <v>1218</v>
       </c>
@@ -39578,7 +39579,7 @@
         <v>91.3</v>
       </c>
     </row>
-    <row r="965" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A965" s="1" t="s">
         <v>1214</v>
       </c>
@@ -39616,7 +39617,7 @@
         <v>48.8</v>
       </c>
     </row>
-    <row r="966" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="966" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F966" s="1" t="s">
         <v>93</v>
       </c>
@@ -39636,7 +39637,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="967" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="967" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F967" s="1" t="s">
         <v>1218</v>
       </c>
@@ -39656,7 +39657,7 @@
         <v>48.8</v>
       </c>
     </row>
-    <row r="968" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="968" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A968" s="1" t="s">
         <v>1214</v>
       </c>
@@ -39694,7 +39695,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="969" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F969" s="1" t="s">
         <v>93</v>
       </c>
@@ -39714,7 +39715,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="970" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="970" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F970" s="1" t="s">
         <v>1218</v>
       </c>
@@ -39734,7 +39735,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="971" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="971" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F971" s="1" t="s">
         <v>93</v>
       </c>
@@ -39754,7 +39755,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="972" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="972" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F972" s="1" t="s">
         <v>1232</v>
       </c>
@@ -39774,7 +39775,7 @@
         <v>1300.5</v>
       </c>
     </row>
-    <row r="973" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="973" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F973" s="1" t="s">
         <v>93</v>
       </c>
@@ -39794,7 +39795,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="974" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="974" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F974" s="1" t="s">
         <v>1233</v>
       </c>
@@ -39814,7 +39815,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="975" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="975" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F975" s="1" t="s">
         <v>93</v>
       </c>
@@ -39838,4 +39839,19 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3307276F-DC7F-48BA-897E-F03E2D904C30}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1">
+        <v>47026</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>